--- a/meta_analysis_shiny/data/quality_coding_clean.xlsx
+++ b/meta_analysis_shiny/data/quality_coding_clean.xlsx
@@ -1,1021 +1,1033 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <workbookPr date1904="false"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\smprchan\Documents\R Programming\agewell_tudo\AgeYouth\meta_analysis_shiny\data\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DB9DE6E-DE33-4802-89C2-FBEB76B89C6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="13125" windowHeight="6105" firstSheet="0" activeTab="0"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet 1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet 1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <calcPr calcId="0"/>
+  <extLst>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="332" uniqueCount="332">
-  <si>
-    <t xml:space="preserve">0_IDF</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1_ID</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2_Author</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3_Year</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4_Title</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1_Qaim</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2_Qpar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3_Qrep</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5_AgrRep</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6_Qdat</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7_Qmeasure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8_Qconf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9_Qsat</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10_Qarr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11_Qmiss</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12_Qmisshan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13_QconS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14_Qfind</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15_Sam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bae</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The relationship between smartphone use for communication, social capital, latent growth modeling</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">unable to determine</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">no</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Random Probability sample</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Casali et al.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Keep going, keep growing: A longitudinal analysis of grit, posttraumatic growth, and life satisfaction in school students under COVID-19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">No</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cha &amp; Yang</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The longitudinal mediating effects of perceived parental neglect on changes on korean adolescents' life satisfaction by gender</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Partly (&gt;=60%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">not random probability Sample</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chen et al.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Peer relationship profiles in rural Chinese adolescents: Longitudinal relations with subjective well-ebing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Boer et al.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The course of problematic social media use in young adolescents: A latent class growth analysis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Borghuis et al.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Longitudinal Associations between trait neuroticism and negative daily experiences in adolescence</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Burris et al.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A longitudinal study of the reciprocal relationship between ever smoking and urgency in early adolescence</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Calandri &amp; Graziano</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Importance of religion and subjective well-being among Italian adolescents: The mediating role of positivity and the moderating role of age</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Daly</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cross-national and longitudinal evidence for a rapid decline in life satisfaction in adolescence</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Daniel et al.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Social identification and well-being following a terrorist attack: A longitudina study of Israelo adolescents</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dion et al.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Changes in Canadian adolescent well-being since the COVID-19 pandemic: The role of prior child maltreatment</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Duncan et al.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The association of physical activity, sleep, and screen time with mental health in Canadian adolescents during the COVID-19 pandemic: A longitudinal isotemporal substitution analysis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Endo et al.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dog and cat ownership predicts adolescents' mental well-being: A population-based longitudinal study</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Esteban-Gonzalo et al.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Diet quality and well-being in children and adolescents: The UP&amp;Down longitudinal study</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A longitudinal gender perspective of well-being and health in spanisch youth: The UP &amp; DOWN study</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fomina et al.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Self-regulation and psychological well-being in early adolescence: A two-wave longitudinal study</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Frison et al.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The short-term longitudinal and reciprocal relations between peer victimization on Facebook and adolescents' well-being</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Galla et al.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The mindful adolescent: Developmental changes in nonreactivity to inner experiences and ist association with emotional well-being</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gomez-Baya et al.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Responses to positive affect, life satisfaction and self-esteem: A cross-lagged panel analysis during middle adolescence</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The prospective relationship of sport and physical activity with life satisfaction after a one-year follow-up: An examination of gender differences during mid-adolescence</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gómez-López et al.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Psychological well-ebing and social competence during adolescence: Longitudinal association between the two phenomena</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Good &amp; Willoughby</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Institutional and personal spirituality/religiosity and pschosocial adjustment in adolescence: Concurrent ans longitudinal association</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Goto et al.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Time trends in emotional well-being and self-esteem in children and adolescents during the COVID-19 pandemic</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Griffith et al.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Affective development from middle childhood to late adolescence: Trajectories of mean-level change in negative ans positive affect</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Griffith &amp; Hankin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Longitudinal coupling of emotional wellbeing in parent-adolescent dyads: Evaluating the role of daily life positive affect socialization processes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Longitudinal associations between positive affect and relationship quality among children and adolescents: Examining patterns of co-occurring change</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Guo et al.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Placing adolescents on a trajectory to happiness: The role of family assets and international self-regulation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hatano et al.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Patterns of personality development and psychosocial funtioning in Japanese adolescents: A four-wave longitudinal study</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hatano &amp; Sugimura</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Is adolescence a period of identity formation for all youth? Insights from a four-wave longitudinal study of identity dynamics in Japan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Huebner &amp; Funk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cross-sectional and longitudinal psychosocial correlates of adolescent life satisfaction reports</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jhang</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The five dimensions of money attitudes and their link to changes in life satisfaction among Taiwanese adolescents in poverty</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jiang et al.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Longitudinal associationsbetween emotion regulation strategies and subjective well-being in migrant and non-migrant adolescents in urban China</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kalak et al.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sleep duration and subjective psychological well-being in adolescence: A longitudinal study in Switzerland and Norway</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kassis et al.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Patterns of students' well-being in early adolescence: A latent class and two-wave latent transition analysis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kim &amp; Jeong</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dynamics of adolescents' life satisfaction and effect of class rank percentile: Evidence from Korean panel data</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kim &amp; Nho</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Longitudinal reciprocal relationships between self-esteem, family support, and life satisfaction in Korean multicultural adolescents</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kim et al.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Role of social capital in adolescents' online gaming: A longitudinal study focused on the moderating effect of social capital between gaming time and psychosocial factors</t>
-  </si>
-  <si>
-    <t xml:space="preserve">How do time use and social relationships affect the life satisfaction trajectory of Korean adolescents?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kim &amp; Ahn</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The longitudinal mediating effect of smartphone dependency on the relationship between exercise time and subjective happiness in adolescents</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kirkham et al.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The effect of school bullying on pupils' perceived stress and wellbeing during the covid-19 pandemic: A longitudinal study</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kleinkorres et al.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A longitudinal analysiss of reciprocal relations between students' well-being and academic achievement</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Klik et al.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">School climate, schoolidentification and student outcomes: A longitudinal investigation of student well-being</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kohut &amp; Štulhofer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Is pornography use a risk for adolescent well-being? An examination of temporal relationships in two independent panel samples</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ku</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Development of materialism in adolescence: The longitudinal role of life satisfaction among Chinese youths</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kwok et al.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Longitudinal associations of suicide risk and protective factors among secondary school students in Hong Kong: A network perspective</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kwon et al.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Effects of student-and school-level music concert attendance on subjective well-being: A longitudinal study of Korean adolescents</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lau et al.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Is internet addiction transitory or persistent? Incidence and prospective predictors of remission of internet addiction among Chinese secondary school students</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lazaridis et al.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Adolescents' out-of-school physical activity levels and well-being during the COVID-19 restrictions in Greece: A longitudinal study</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Damian et al.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">On the longitudinal interplay between perfectionism and general affect in adolescents</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kipp &amp; Weiss</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Social predictors of psychological need satisfaction and well-being among female adolescent gymnasts: A longitudinal analysis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lee et al.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reciprocal relationship between multicultural adolescents' depression and life satisfaction: A random intercept cross-lagged panel model for 3-wave data</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Li</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The contributions of Indigenous personality and parenting style to life satisfaction development in Chinese adolescents</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Li et al.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The developmental trajectory of subjective well-being in Chinese early adolescents: The role of gender and parental involvement</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The longitudinal relationship between future time perspective and life satisfaction among Chinese adolescents</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A longitudinal network analysis of the interactions of risk and protective factors for suicidal potential in early adolescents</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The bidirectional relationships between fear of missing out, problematic social media use and adolescents' well-being: A random intercept cross-lagged panel model</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lima et al.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trajectories of adjustment in a Brazil sample of street-involved youth</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lin &amp; Yi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Subjective well-being and family structure during early adolescence: A prospective study</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">De Lise et al.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Identity matters for well-being: The longitudinal associations between identity processes and well-being in adolescents with different cultural backgrounds</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Liu et al.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Longitudinal relationship between quality of life and negative life events among adolescents during COVID-19 pandemic: A cross-lagged panel analysis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Luijten et al.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Longitudinal associations among adolescents' internalizing problems, well-being, and the quality of their relationships with their mothers, fathers, and close friends</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Adolescents' friendship quality and over-time development of well-being: The explanatory role of self-esteem</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lyons &amp; Jiang</t>
-  </si>
-  <si>
-    <t xml:space="preserve">School-related social support as a buffer to stressors i the development od adolescent life satisfaction</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Maciejewski et al.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A 5-year longitudinal study on mood variability across adolescence using daily diaries</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Magson et al.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Risk an protective factors for prospective changes in adolescent mental health during the COVID-19 Pandemic</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Examining the prospective bidirectional associations between subjective and objective atttractiveness and adolescent internalizing symptoms and life satisfaction</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Marcionetti &amp; Rossier</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A longitudinal study of relatins among adolescents' self-esteem, general self-efficacy, career adaptability, and life satisfaction</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Marques et al.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The role of hope, spirituality and religious practice in adolescents' Life Satisfaction: Longitudinal findings</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The role of positive psychology constructs in predicting mental health and academic achievement in children and adolescents: A two-year longitudinal study</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mason &amp; Spoth</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Longitudinal associations of alcohol involvement with subjective well-being in adolescence and prediction to alcohol problems in early adulthood</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Matić &amp; Musil</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Subjective wll-being and self-assessed health of adolescents: A longitudinal cohort study</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Meade &amp; Dowswell</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Adolescents' health-relate quality of life (HRQoL) changes over time: A three year longitudinal study</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mikkelsen et al.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Changes in health-related quality of life in adolescents and the impact of gender and selected variables: A two-year longitudinal study</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mitchell et al.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Narrative coherence, psychopathology, and wellbeing: Concurrent and longitudinal findings in a mid-adolescent sample</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nießen et al.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aspiration-attainment gaps predict adolescents' subjective well-being after transition to vocational education and training in Germany</t>
-  </si>
-  <si>
-    <t xml:space="preserve">O'Donnell et al.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trajectories of substance use and well-being in early and middle adolescence shaped by social connectedness</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Oriol &amp; Miranda</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The prospective relationships between dispositional optimism and subjective and psychological well-being in children and adolescents</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Papaioannou &amp; Siskos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Changes in achievement goals and self-concpet in the eraly months of junior high school</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Park</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Examining trajectories of early adolescents' life satisfaction in South Korea using a growth mixture model</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Parra et al.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Development of emotional autonomy from adolescence to young adulthood in Spain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Poon et al.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Delayed gratification and psychosocial wellbeing among high-risk youth in rehabilitation: A latent change score analysis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prati et al.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Developmental relations between sense of community and well-being among early adolescents: A latent change score modelling study</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Saha et al.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A Longitudinal Study of Adolescent Life Satisfaction and Parenting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Salmela-Aro &amp; Tuominen-Soini</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Adolescents’ Life Satisfaction During the Transition to Post-Comprehensive Education: Antecedents and Consequences</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Salmela-Aro &amp; Tynkkynen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trajectories of Life Satisfaction Across the Transition to Post-Compulsory Education: Do Adolescents Follow Different Pathways?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Salonna et al.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Deterioration Is Not the Only Prospect for Adolescents’ Health: Improvement in Self-reported Health Status Among Boys and Girls From Age 15 to Age 19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sánchez-Álvarez et al.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Maintaining Life Satisfaction in Adolescence: Affective Mediators of the Influence of Perceived Emotional Intelligence on Overall Life Satisfaction Judgments in a Two -Year Longitudinal Study</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sanchez-Alvarez et al.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The influence of trait meta-mood on subjective well-being in high school students: a random intercept cross-lagged panel analysis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Seaton et al.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Status Model of Racial Identity Development in African American Adolescents: Evidence of Structure, Trajectories, and Well-Being</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shek</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A Longitudinal Study of Perceived Parental Psychological Control and Psychological Well-Being in Chinese Adolescents in Hong Kong</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shek &amp; Li</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Perceived School Performance, Life Satisfaction, and Hopelessness: A 4-Year Longitudinal Study of Adolescents in Hong Kong</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shek &amp; Liu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Life Satisfaction in Junior Secondary School Students in Hong Kong: A 3-Year Longitudinal Study</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shi et al.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Investigating the Trajectory of Mexican-Origin Youth’s Materialistic Values Across Adolescence and Prospective Associations With Life Satisfaction in Early Adulthood: The Role of Familism, Demographic Factors, and Parent Characteristics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shoshani &amp; Slone</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Middle School Transition from the Strengths Perspective: Young Adolescents’ Character Strengths, Subjective Well-Being, and School Adjustment</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Spiegler et al.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dual Identity Development and Adjustment in Muslim Minority Adolescents</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Steinmayr et al.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Development of Subjective Well-Being in Adolescence</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unable to determine</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stevens et al.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Examining socioeconomic disparities in changes in adolescent mental health before and during different phases of the coronavirus disease 2019 pandemic</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thomsen et al.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The impact of accommodative coping on well-being in childhood and adolescence: Longitudinal findings</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tumminia et al.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">How is Mindfulness Linked to Negative and Positive Affect? Rumination as an Explanatory Process in a Prospective Longitudinal Study of Adolescents</t>
-  </si>
-  <si>
-    <t xml:space="preserve">van der Laan et al.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gender-Specific Changes in Life Satisfaction After the COVID-19eRelated Lockdown in Dutch Adolescents: A Longitudinal Study</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wang et al.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Life satisfaction trajectories among junior high school students in China: The role of parent–child communication</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weber et al.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Individual Development of Cultural Identity and Psychological Well-Being Among Adolescents With a Migrant Background in Austria:A Longitudinal Study</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wiglesworth et al.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stress system concordance as a predictor of longitudinal patterns of resilience in adolescence</t>
-  </si>
-  <si>
-    <t xml:space="preserve">yes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Willroth et al.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Life Satisfaction Trajectories During Adolescence and the Transition to Young Adulthood: Findings From a Longitudinal Study of Mexican-Origin Youth</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wu &amp; Becker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Association between school context and the development of subjective well-being during adolescence: A context-sensitive longitudinal study of life satisfaction and school satisfaction</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yiang et al.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Development of self-concept clarity from ages 11 to 24: Latent growth models of Chinese adolescents</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Xiong et al.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Does being prosocial psy off? Testing positive developmental cascades of prosocial behavior, social preference, and aubjective well-being in Chinese adolescents</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zhang et al.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The role of affect in the positive self: Two longitudinal investigations of young adolescents in the United States and China</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Adie et al.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Achievement goals, competition appraisals, and the well- and ill-being of elite youth soccer players over two competitve seasons</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Armeta et al.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A longitudinal examiniation of the measurement properties and predictive utility of the Center for Epidemiologic Studies Depression scale among North American indigenous adolescents</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bearman et al.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The skinny on body dissatisfaction: A longitudinal study of adolescent girls and boys</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bergold &amp; Steinmayr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Teacher judgements predict developments in adolescents' school performance, motivation, and life satisfaction</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Burger &amp; Samuel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The role of perceived stress and self-efficacy in young people's life satisfaction: A longitudinal study</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chen &amp; Cheng</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Developmental trajectory of purpose identification during adolescence: Links to life satisfaction and depressice symptoms</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chen &amp; Jackson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Predictors of changes in nody image concerns of Chinese adolescents</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Subjective poverty, deprivation, and the subjective well-being of children and young people: A multilevel growth curve analysis in Taiwan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Purpose trajectories during middle adolescence: The role of family, teacher, and peer support</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Delfabbro et al.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Factors associated with attrition in a 10-year longitudinal study of young people: Implications for studies of emplyment in school leavers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dill et al.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Negative affect in vicitimized children: The roles of social withdrawal, peer rejection, and attitudes toward bullying</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Duineveld et al.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The link between perceived maternal and paternal autonomy support and adolescent well-being across three major educational transitions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fosco &amp; Feinberg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cascading effects of interparental conflict in adolescence: Limking threat appraisals, self-efficacy, and adjustment</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gerber et al.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Adolescents with high mental toughness adapt better to perceived stress: A longitudinal study with Swiss vocational students</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gillham et al.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Character strengths predict subjective well-being during adolescence</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haase et al.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Happiness as a motivator: Positive affect predicts primary control striving for career and educational goals</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haraden et al.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Internalizing symptoms and chronotype in youth: A longitudinal assessment of anxiety, depression and tripartite model</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trajectories in sense of identity and relationship with life satisfaction during adolescence and young adulthood</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jackson &amp; Chen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Risk factors for disordered eating during early and middle adolescence: A two year longitudinal study of mainland Chinese boys and girls</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cumulative risk and subjective well-being among rural-to-urban migrant adolescents in China: Differential moderating roles of stressmindset and resilience</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jose et al.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Does social connectedness promote a greater sense of well-being in adolescence over time?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jung &amp; Choi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Life satisfaction and delinquent behaviors among Korean adolescents</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Liem et al.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Depressive Symptoms and Life Satisfaction Among Emerging Adults: A Comparison of High School Dropouts and Graduates</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Effect of Family Cohesion and Life Satisfaction During Adolescence on Later Adolescent Outcomes:A Prospective Study</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Marques</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Psychological Strengths in Childhood as Predictors of Longitudinal Outcomes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Martin et al.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Role of Arts Participation in Students’ Academic and Nonacademic Outcomes: A Longitudinal Study of School, Home, and Community Factors</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sample recruitment</t>
-  </si>
-  <si>
-    <t xml:space="preserve">McCabe &amp; Ricciardelli</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A Prospective Study of ExtremeWeight Change Behaviors Among Adolescent Boys and Girls</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extreme Weight Change Behaviours: Are Overweight and Normal Weight Adolescents Different, and Does this Vary Over Time?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Miller et al.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The role of negative affect in the persistence of nicotine dependence among alternative high school students: A latent growth curve analysis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ricciardelli et al.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A Longitudinal Investigation of the Development of Weight and Muscle Concerns Among Preadolescent Boys</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Richmond et al.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Direct Observations of Parenting and Real-time Negative Affect among Adolescent Smokers and Non-Smokers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shoshani et al.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Effects of the Maytiv positive psychology school program on early adolescents' well-being, engagement, and achievement</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Song et al.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pathways Linking Ethnic Discrimination and Drug-Using Peer Affiliation to Underage Drinking Status Among Mexican-Origin Adolescents</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Su et al.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Future Orientation, Social Support, and Psychological Adjustment among Left-behind Children in Rural China: A Longitudinal Study</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Suldo &amp; Huebner</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Does Life Satisfaction Moderate the Effects of Stressful Life Events on Psychopathological Behavior During Adolescence?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sun &amp; Shek</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Longitudinal Influences of Positive Youth Development and Life Satisfaction on Problem Behaviour among Adolescents in Hong Kong</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Teng et al.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Internet gaming disorder and psychosocial well-being: A longitudinal study of older-aged adolescents and emerging adults</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Valle et al.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">An analysis of hope as a psychological strength</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Van Den Eijnden et al.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The impact of heavy and disordered use of games and social media on adolescents’ psychological, social, and school functioning</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weinstein et al.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Time-Varying Influences of Peer and Family Support on Adolescent Daily Positive and Negative Affect</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Life Satisfaction Trajectories during Adolescence and the Transition to Young Adulthood: Findings from a Longitudinal Study of Mexican-origin Youth</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The relations of migrant status and parenting to Chinese adolescents’ adjustment</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zhu &amp; Shek</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Predictive Effect of Positive Youth Development Attributes on Delinquency Among Adolescents in Mainland China</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Parental factors and adolescent well-being: Associations between developmental trajectories</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2603" uniqueCount="332">
+  <si>
+    <t>0_IDF</t>
+  </si>
+  <si>
+    <t>1_ID</t>
+  </si>
+  <si>
+    <t>2_Author</t>
+  </si>
+  <si>
+    <t>3_Year</t>
+  </si>
+  <si>
+    <t>4_Title</t>
+  </si>
+  <si>
+    <t>1_Qaim</t>
+  </si>
+  <si>
+    <t>2_Qpar</t>
+  </si>
+  <si>
+    <t>3_Qrep</t>
+  </si>
+  <si>
+    <t>5_AgrRep</t>
+  </si>
+  <si>
+    <t>6_Qdat</t>
+  </si>
+  <si>
+    <t>7_Qmeasure</t>
+  </si>
+  <si>
+    <t>8_Qconf</t>
+  </si>
+  <si>
+    <t>9_Qsat</t>
+  </si>
+  <si>
+    <t>10_Qarr</t>
+  </si>
+  <si>
+    <t>11_Qmiss</t>
+  </si>
+  <si>
+    <t>12_Qmisshan</t>
+  </si>
+  <si>
+    <t>13_QconS</t>
+  </si>
+  <si>
+    <t>14_Qfind</t>
+  </si>
+  <si>
+    <t>15_Sam</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>Bae</t>
+  </si>
+  <si>
+    <t>The relationship between smartphone use for communication, social capital, latent growth modeling</t>
+  </si>
+  <si>
+    <t>Yes</t>
+  </si>
+  <si>
+    <t>unable to determine</t>
+  </si>
+  <si>
+    <t>NA</t>
+  </si>
+  <si>
+    <t>no</t>
+  </si>
+  <si>
+    <t>Random Probability sample</t>
+  </si>
+  <si>
+    <t>2.1</t>
+  </si>
+  <si>
+    <t>Casali et al.</t>
+  </si>
+  <si>
+    <t>Keep going, keep growing: A longitudinal analysis of grit, posttraumatic growth, and life satisfaction in school students under COVID-19</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>Cha &amp; Yang</t>
+  </si>
+  <si>
+    <t>The longitudinal mediating effects of perceived parental neglect on changes on korean adolescents' life satisfaction by gender</t>
+  </si>
+  <si>
+    <t>Partly (&gt;=60%)</t>
+  </si>
+  <si>
+    <t>not random probability Sample</t>
+  </si>
+  <si>
+    <t>Chen et al.</t>
+  </si>
+  <si>
+    <t>Peer relationship profiles in rural Chinese adolescents: Longitudinal relations with subjective well-ebing</t>
+  </si>
+  <si>
+    <t>2.2</t>
+  </si>
+  <si>
+    <t>Boer et al.</t>
+  </si>
+  <si>
+    <t>The course of problematic social media use in young adolescents: A latent class growth analysis</t>
+  </si>
+  <si>
+    <t>Borghuis et al.</t>
+  </si>
+  <si>
+    <t>Longitudinal Associations between trait neuroticism and negative daily experiences in adolescence</t>
+  </si>
+  <si>
+    <t>Burris et al.</t>
+  </si>
+  <si>
+    <t>A longitudinal study of the reciprocal relationship between ever smoking and urgency in early adolescence</t>
+  </si>
+  <si>
+    <t>Calandri &amp; Graziano</t>
+  </si>
+  <si>
+    <t>Importance of religion and subjective well-being among Italian adolescents: The mediating role of positivity and the moderating role of age</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>Daly</t>
+  </si>
+  <si>
+    <t>Cross-national and longitudinal evidence for a rapid decline in life satisfaction in adolescence</t>
+  </si>
+  <si>
+    <t>Daniel et al.</t>
+  </si>
+  <si>
+    <t>Social identification and well-being following a terrorist attack: A longitudina study of Israelo adolescents</t>
+  </si>
+  <si>
+    <t>Dion et al.</t>
+  </si>
+  <si>
+    <t>Changes in Canadian adolescent well-being since the COVID-19 pandemic: The role of prior child maltreatment</t>
+  </si>
+  <si>
+    <t>Duncan et al.</t>
+  </si>
+  <si>
+    <t>The association of physical activity, sleep, and screen time with mental health in Canadian adolescents during the COVID-19 pandemic: A longitudinal isotemporal substitution analysis</t>
+  </si>
+  <si>
+    <t>Endo et al.</t>
+  </si>
+  <si>
+    <t>Dog and cat ownership predicts adolescents' mental well-being: A population-based longitudinal study</t>
+  </si>
+  <si>
+    <t>Esteban-Gonzalo et al.</t>
+  </si>
+  <si>
+    <t>Diet quality and well-being in children and adolescents: The UP&amp;Down longitudinal study</t>
+  </si>
+  <si>
+    <t>A longitudinal gender perspective of well-being and health in spanisch youth: The UP &amp; DOWN study</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>Fomina et al.</t>
+  </si>
+  <si>
+    <t>Self-regulation and psychological well-being in early adolescence: A two-wave longitudinal study</t>
+  </si>
+  <si>
+    <t>Frison et al.</t>
+  </si>
+  <si>
+    <t>The short-term longitudinal and reciprocal relations between peer victimization on Facebook and adolescents' well-being</t>
+  </si>
+  <si>
+    <t>Galla et al.</t>
+  </si>
+  <si>
+    <t>The mindful adolescent: Developmental changes in nonreactivity to inner experiences and ist association with emotional well-being</t>
+  </si>
+  <si>
+    <t>Gomez-Baya et al.</t>
+  </si>
+  <si>
+    <t>Responses to positive affect, life satisfaction and self-esteem: A cross-lagged panel analysis during middle adolescence</t>
+  </si>
+  <si>
+    <t>The prospective relationship of sport and physical activity with life satisfaction after a one-year follow-up: An examination of gender differences during mid-adolescence</t>
+  </si>
+  <si>
+    <t>Gómez-López et al.</t>
+  </si>
+  <si>
+    <t>Psychological well-ebing and social competence during adolescence: Longitudinal association between the two phenomena</t>
+  </si>
+  <si>
+    <t>Good &amp; Willoughby</t>
+  </si>
+  <si>
+    <t>Institutional and personal spirituality/religiosity and pschosocial adjustment in adolescence: Concurrent ans longitudinal association</t>
+  </si>
+  <si>
+    <t>Goto et al.</t>
+  </si>
+  <si>
+    <t>Time trends in emotional well-being and self-esteem in children and adolescents during the COVID-19 pandemic</t>
+  </si>
+  <si>
+    <t>Griffith et al.</t>
+  </si>
+  <si>
+    <t>Affective development from middle childhood to late adolescence: Trajectories of mean-level change in negative ans positive affect</t>
+  </si>
+  <si>
+    <t>Griffith &amp; Hankin</t>
+  </si>
+  <si>
+    <t>Longitudinal coupling of emotional wellbeing in parent-adolescent dyads: Evaluating the role of daily life positive affect socialization processes</t>
+  </si>
+  <si>
+    <t>Longitudinal associations between positive affect and relationship quality among children and adolescents: Examining patterns of co-occurring change</t>
+  </si>
+  <si>
+    <t>Guo et al.</t>
+  </si>
+  <si>
+    <t>Placing adolescents on a trajectory to happiness: The role of family assets and international self-regulation</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>Hatano et al.</t>
+  </si>
+  <si>
+    <t>Patterns of personality development and psychosocial funtioning in Japanese adolescents: A four-wave longitudinal study</t>
+  </si>
+  <si>
+    <t>Hatano &amp; Sugimura</t>
+  </si>
+  <si>
+    <t>Is adolescence a period of identity formation for all youth? Insights from a four-wave longitudinal study of identity dynamics in Japan</t>
+  </si>
+  <si>
+    <t>Huebner &amp; Funk</t>
+  </si>
+  <si>
+    <t>Cross-sectional and longitudinal psychosocial correlates of adolescent life satisfaction reports</t>
+  </si>
+  <si>
+    <t>Jhang</t>
+  </si>
+  <si>
+    <t>The five dimensions of money attitudes and their link to changes in life satisfaction among Taiwanese adolescents in poverty</t>
+  </si>
+  <si>
+    <t>Jiang et al.</t>
+  </si>
+  <si>
+    <t>Longitudinal associationsbetween emotion regulation strategies and subjective well-being in migrant and non-migrant adolescents in urban China</t>
+  </si>
+  <si>
+    <t>Kalak et al.</t>
+  </si>
+  <si>
+    <t>Sleep duration and subjective psychological well-being in adolescence: A longitudinal study in Switzerland and Norway</t>
+  </si>
+  <si>
+    <t>Kassis et al.</t>
+  </si>
+  <si>
+    <t>Patterns of students' well-being in early adolescence: A latent class and two-wave latent transition analysis</t>
+  </si>
+  <si>
+    <t>6.1</t>
+  </si>
+  <si>
+    <t>Kim &amp; Jeong</t>
+  </si>
+  <si>
+    <t>Dynamics of adolescents' life satisfaction and effect of class rank percentile: Evidence from Korean panel data</t>
+  </si>
+  <si>
+    <t>Kim &amp; Nho</t>
+  </si>
+  <si>
+    <t>Longitudinal reciprocal relationships between self-esteem, family support, and life satisfaction in Korean multicultural adolescents</t>
+  </si>
+  <si>
+    <t>Kim et al.</t>
+  </si>
+  <si>
+    <t>Role of social capital in adolescents' online gaming: A longitudinal study focused on the moderating effect of social capital between gaming time and psychosocial factors</t>
+  </si>
+  <si>
+    <t>How do time use and social relationships affect the life satisfaction trajectory of Korean adolescents?</t>
+  </si>
+  <si>
+    <t>Kim &amp; Ahn</t>
+  </si>
+  <si>
+    <t>The longitudinal mediating effect of smartphone dependency on the relationship between exercise time and subjective happiness in adolescents</t>
+  </si>
+  <si>
+    <t>Kirkham et al.</t>
+  </si>
+  <si>
+    <t>The effect of school bullying on pupils' perceived stress and wellbeing during the covid-19 pandemic: A longitudinal study</t>
+  </si>
+  <si>
+    <t>Kleinkorres et al.</t>
+  </si>
+  <si>
+    <t>A longitudinal analysiss of reciprocal relations between students' well-being and academic achievement</t>
+  </si>
+  <si>
+    <t>Klik et al.</t>
+  </si>
+  <si>
+    <t>School climate, schoolidentification and student outcomes: A longitudinal investigation of student well-being</t>
+  </si>
+  <si>
+    <t>Kohut &amp; Štulhofer</t>
+  </si>
+  <si>
+    <t>Is pornography use a risk for adolescent well-being? An examination of temporal relationships in two independent panel samples</t>
+  </si>
+  <si>
+    <t>Ku</t>
+  </si>
+  <si>
+    <t>Development of materialism in adolescence: The longitudinal role of life satisfaction among Chinese youths</t>
+  </si>
+  <si>
+    <t>Kwok et al.</t>
+  </si>
+  <si>
+    <t>Longitudinal associations of suicide risk and protective factors among secondary school students in Hong Kong: A network perspective</t>
+  </si>
+  <si>
+    <t>Kwon et al.</t>
+  </si>
+  <si>
+    <t>Effects of student-and school-level music concert attendance on subjective well-being: A longitudinal study of Korean adolescents</t>
+  </si>
+  <si>
+    <t>6.2</t>
+  </si>
+  <si>
+    <t>Lau et al.</t>
+  </si>
+  <si>
+    <t>Is internet addiction transitory or persistent? Incidence and prospective predictors of remission of internet addiction among Chinese secondary school students</t>
+  </si>
+  <si>
+    <t>Lazaridis et al.</t>
+  </si>
+  <si>
+    <t>Adolescents' out-of-school physical activity levels and well-being during the COVID-19 restrictions in Greece: A longitudinal study</t>
+  </si>
+  <si>
+    <t>Damian et al.</t>
+  </si>
+  <si>
+    <t>On the longitudinal interplay between perfectionism and general affect in adolescents</t>
+  </si>
+  <si>
+    <t>Kipp &amp; Weiss</t>
+  </si>
+  <si>
+    <t>Social predictors of psychological need satisfaction and well-being among female adolescent gymnasts: A longitudinal analysis</t>
+  </si>
+  <si>
+    <t>Lee et al.</t>
+  </si>
+  <si>
+    <t>Reciprocal relationship between multicultural adolescents' depression and life satisfaction: A random intercept cross-lagged panel model for 3-wave data</t>
+  </si>
+  <si>
+    <t>Li</t>
+  </si>
+  <si>
+    <t>The contributions of Indigenous personality and parenting style to life satisfaction development in Chinese adolescents</t>
+  </si>
+  <si>
+    <t>Li et al.</t>
+  </si>
+  <si>
+    <t>The developmental trajectory of subjective well-being in Chinese early adolescents: The role of gender and parental involvement</t>
+  </si>
+  <si>
+    <t>The longitudinal relationship between future time perspective and life satisfaction among Chinese adolescents</t>
+  </si>
+  <si>
+    <t>A longitudinal network analysis of the interactions of risk and protective factors for suicidal potential in early adolescents</t>
+  </si>
+  <si>
+    <t>The bidirectional relationships between fear of missing out, problematic social media use and adolescents' well-being: A random intercept cross-lagged panel model</t>
+  </si>
+  <si>
+    <t>Lima et al.</t>
+  </si>
+  <si>
+    <t>Trajectories of adjustment in a Brazil sample of street-involved youth</t>
+  </si>
+  <si>
+    <t>Lin &amp; Yi</t>
+  </si>
+  <si>
+    <t>Subjective well-being and family structure during early adolescence: A prospective study</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>De Lise et al.</t>
+  </si>
+  <si>
+    <t>Identity matters for well-being: The longitudinal associations between identity processes and well-being in adolescents with different cultural backgrounds</t>
+  </si>
+  <si>
+    <t>Liu et al.</t>
+  </si>
+  <si>
+    <t>Longitudinal relationship between quality of life and negative life events among adolescents during COVID-19 pandemic: A cross-lagged panel analysis</t>
+  </si>
+  <si>
+    <t>Luijten et al.</t>
+  </si>
+  <si>
+    <t>Longitudinal associations among adolescents' internalizing problems, well-being, and the quality of their relationships with their mothers, fathers, and close friends</t>
+  </si>
+  <si>
+    <t>Adolescents' friendship quality and over-time development of well-being: The explanatory role of self-esteem</t>
+  </si>
+  <si>
+    <t>Lyons &amp; Jiang</t>
+  </si>
+  <si>
+    <t>School-related social support as a buffer to stressors i the development od adolescent life satisfaction</t>
+  </si>
+  <si>
+    <t>Maciejewski et al.</t>
+  </si>
+  <si>
+    <t>A 5-year longitudinal study on mood variability across adolescence using daily diaries</t>
+  </si>
+  <si>
+    <t>Magson et al.</t>
+  </si>
+  <si>
+    <t>Risk an protective factors for prospective changes in adolescent mental health during the COVID-19 Pandemic</t>
+  </si>
+  <si>
+    <t>Examining the prospective bidirectional associations between subjective and objective atttractiveness and adolescent internalizing symptoms and life satisfaction</t>
+  </si>
+  <si>
+    <t>Marcionetti &amp; Rossier</t>
+  </si>
+  <si>
+    <t>A longitudinal study of relatins among adolescents' self-esteem, general self-efficacy, career adaptability, and life satisfaction</t>
+  </si>
+  <si>
+    <t>Marques et al.</t>
+  </si>
+  <si>
+    <t>The role of hope, spirituality and religious practice in adolescents' Life Satisfaction: Longitudinal findings</t>
+  </si>
+  <si>
+    <t>The role of positive psychology constructs in predicting mental health and academic achievement in children and adolescents: A two-year longitudinal study</t>
+  </si>
+  <si>
+    <t>Mason &amp; Spoth</t>
+  </si>
+  <si>
+    <t>Longitudinal associations of alcohol involvement with subjective well-being in adolescence and prediction to alcohol problems in early adulthood</t>
+  </si>
+  <si>
+    <t>Matić &amp; Musil</t>
+  </si>
+  <si>
+    <t>Subjective wll-being and self-assessed health of adolescents: A longitudinal cohort study</t>
+  </si>
+  <si>
+    <t>Meade &amp; Dowswell</t>
+  </si>
+  <si>
+    <t>Adolescents' health-relate quality of life (HRQoL) changes over time: A three year longitudinal study</t>
+  </si>
+  <si>
+    <t>Mikkelsen et al.</t>
+  </si>
+  <si>
+    <t>Changes in health-related quality of life in adolescents and the impact of gender and selected variables: A two-year longitudinal study</t>
+  </si>
+  <si>
+    <t>Mitchell et al.</t>
+  </si>
+  <si>
+    <t>Narrative coherence, psychopathology, and wellbeing: Concurrent and longitudinal findings in a mid-adolescent sample</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>Nießen et al.</t>
+  </si>
+  <si>
+    <t>Aspiration-attainment gaps predict adolescents' subjective well-being after transition to vocational education and training in Germany</t>
+  </si>
+  <si>
+    <t>O'Donnell et al.</t>
+  </si>
+  <si>
+    <t>Trajectories of substance use and well-being in early and middle adolescence shaped by social connectedness</t>
+  </si>
+  <si>
+    <t>Oriol &amp; Miranda</t>
+  </si>
+  <si>
+    <t>The prospective relationships between dispositional optimism and subjective and psychological well-being in children and adolescents</t>
+  </si>
+  <si>
+    <t>Papaioannou &amp; Siskos</t>
+  </si>
+  <si>
+    <t>Changes in achievement goals and self-concpet in the eraly months of junior high school</t>
+  </si>
+  <si>
+    <t>Park</t>
+  </si>
+  <si>
+    <t>Examining trajectories of early adolescents' life satisfaction in South Korea using a growth mixture model</t>
+  </si>
+  <si>
+    <t>Parra et al.</t>
+  </si>
+  <si>
+    <t>Development of emotional autonomy from adolescence to young adulthood in Spain</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>Poon et al.</t>
+  </si>
+  <si>
+    <t>Delayed gratification and psychosocial wellbeing among high-risk youth in rehabilitation: A latent change score analysis</t>
+  </si>
+  <si>
+    <t>Prati et al.</t>
+  </si>
+  <si>
+    <t>Developmental relations between sense of community and well-being among early adolescents: A latent change score modelling study</t>
+  </si>
+  <si>
+    <t>Saha et al.</t>
+  </si>
+  <si>
+    <t>A Longitudinal Study of Adolescent Life Satisfaction and Parenting</t>
+  </si>
+  <si>
+    <t>Salmela-Aro &amp; Tuominen-Soini</t>
+  </si>
+  <si>
+    <t>Adolescents’ Life Satisfaction During the Transition to Post-Comprehensive Education: Antecedents and Consequences</t>
+  </si>
+  <si>
+    <t>Salmela-Aro &amp; Tynkkynen</t>
+  </si>
+  <si>
+    <t>Trajectories of Life Satisfaction Across the Transition to Post-Compulsory Education: Do Adolescents Follow Different Pathways?</t>
+  </si>
+  <si>
+    <t>Salonna et al.</t>
+  </si>
+  <si>
+    <t>Deterioration Is Not the Only Prospect for Adolescents’ Health: Improvement in Self-reported Health Status Among Boys and Girls From Age 15 to Age 19</t>
+  </si>
+  <si>
+    <t>Sánchez-Álvarez et al.</t>
+  </si>
+  <si>
+    <t>Maintaining Life Satisfaction in Adolescence: Affective Mediators of the Influence of Perceived Emotional Intelligence on Overall Life Satisfaction Judgments in a Two -Year Longitudinal Study</t>
+  </si>
+  <si>
+    <t>Sanchez-Alvarez et al.</t>
+  </si>
+  <si>
+    <t>The influence of trait meta-mood on subjective well-being in high school students: a random intercept cross-lagged panel analysis</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>Seaton et al.</t>
+  </si>
+  <si>
+    <t>The Status Model of Racial Identity Development in African American Adolescents: Evidence of Structure, Trajectories, and Well-Being</t>
+  </si>
+  <si>
+    <t>Shek</t>
+  </si>
+  <si>
+    <t>A Longitudinal Study of Perceived Parental Psychological Control and Psychological Well-Being in Chinese Adolescents in Hong Kong</t>
+  </si>
+  <si>
+    <t>Shek &amp; Li</t>
+  </si>
+  <si>
+    <t>Perceived School Performance, Life Satisfaction, and Hopelessness: A 4-Year Longitudinal Study of Adolescents in Hong Kong</t>
+  </si>
+  <si>
+    <t>Shek &amp; Liu</t>
+  </si>
+  <si>
+    <t>Life Satisfaction in Junior Secondary School Students in Hong Kong: A 3-Year Longitudinal Study</t>
+  </si>
+  <si>
+    <t>Shi et al.</t>
+  </si>
+  <si>
+    <t>Investigating the Trajectory of Mexican-Origin Youth’s Materialistic Values Across Adolescence and Prospective Associations With Life Satisfaction in Early Adulthood: The Role of Familism, Demographic Factors, and Parent Characteristics</t>
+  </si>
+  <si>
+    <t>Shoshani &amp; Slone</t>
+  </si>
+  <si>
+    <t>Middle School Transition from the Strengths Perspective: Young Adolescents’ Character Strengths, Subjective Well-Being, and School Adjustment</t>
+  </si>
+  <si>
+    <t>Spiegler et al.</t>
+  </si>
+  <si>
+    <t>Dual Identity Development and Adjustment in Muslim Minority Adolescents</t>
+  </si>
+  <si>
+    <t>Steinmayr et al.</t>
+  </si>
+  <si>
+    <t>Development of Subjective Well-Being in Adolescence</t>
+  </si>
+  <si>
+    <t>Unable to determine</t>
+  </si>
+  <si>
+    <t>Stevens et al.</t>
+  </si>
+  <si>
+    <t>Examining socioeconomic disparities in changes in adolescent mental health before and during different phases of the coronavirus disease 2019 pandemic</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>Thomsen et al.</t>
+  </si>
+  <si>
+    <t>The impact of accommodative coping on well-being in childhood and adolescence: Longitudinal findings</t>
+  </si>
+  <si>
+    <t>Tumminia et al.</t>
+  </si>
+  <si>
+    <t>How is Mindfulness Linked to Negative and Positive Affect? Rumination as an Explanatory Process in a Prospective Longitudinal Study of Adolescents</t>
+  </si>
+  <si>
+    <t>van der Laan et al.</t>
+  </si>
+  <si>
+    <t>Gender-Specific Changes in Life Satisfaction After the COVID-19eRelated Lockdown in Dutch Adolescents: A Longitudinal Study</t>
+  </si>
+  <si>
+    <t>Wang et al.</t>
+  </si>
+  <si>
+    <t>Life satisfaction trajectories among junior high school students in China: The role of parent–child communication</t>
+  </si>
+  <si>
+    <t>Weber et al.</t>
+  </si>
+  <si>
+    <t>The Individual Development of Cultural Identity and Psychological Well-Being Among Adolescents With a Migrant Background in Austria:A Longitudinal Study</t>
+  </si>
+  <si>
+    <t>Wiglesworth et al.</t>
+  </si>
+  <si>
+    <t>Stress system concordance as a predictor of longitudinal patterns of resilience in adolescence</t>
+  </si>
+  <si>
+    <t>yes</t>
+  </si>
+  <si>
+    <t>9999</t>
+  </si>
+  <si>
+    <t>Willroth et al.</t>
+  </si>
+  <si>
+    <t>Life Satisfaction Trajectories During Adolescence and the Transition to Young Adulthood: Findings From a Longitudinal Study of Mexican-Origin Youth</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>Wu &amp; Becker</t>
+  </si>
+  <si>
+    <t>Association between school context and the development of subjective well-being during adolescence: A context-sensitive longitudinal study of life satisfaction and school satisfaction</t>
+  </si>
+  <si>
+    <t>Yiang et al.</t>
+  </si>
+  <si>
+    <t>Development of self-concept clarity from ages 11 to 24: Latent growth models of Chinese adolescents</t>
+  </si>
+  <si>
+    <t>Xiong et al.</t>
+  </si>
+  <si>
+    <t>Does being prosocial psy off? Testing positive developmental cascades of prosocial behavior, social preference, and aubjective well-being in Chinese adolescents</t>
+  </si>
+  <si>
+    <t>Zhang et al.</t>
+  </si>
+  <si>
+    <t>The role of affect in the positive self: Two longitudinal investigations of young adolescents in the United States and China</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>Adie et al.</t>
+  </si>
+  <si>
+    <t>Achievement goals, competition appraisals, and the well- and ill-being of elite youth soccer players over two competitve seasons</t>
+  </si>
+  <si>
+    <t>Armeta et al.</t>
+  </si>
+  <si>
+    <t>A longitudinal examiniation of the measurement properties and predictive utility of the Center for Epidemiologic Studies Depression scale among North American indigenous adolescents</t>
+  </si>
+  <si>
+    <t>Bearman et al.</t>
+  </si>
+  <si>
+    <t>The skinny on body dissatisfaction: A longitudinal study of adolescent girls and boys</t>
+  </si>
+  <si>
+    <t>Bergold &amp; Steinmayr</t>
+  </si>
+  <si>
+    <t>Teacher judgements predict developments in adolescents' school performance, motivation, and life satisfaction</t>
+  </si>
+  <si>
+    <t>Burger &amp; Samuel</t>
+  </si>
+  <si>
+    <t>The role of perceived stress and self-efficacy in young people's life satisfaction: A longitudinal study</t>
+  </si>
+  <si>
+    <t>Chen &amp; Cheng</t>
+  </si>
+  <si>
+    <t>Developmental trajectory of purpose identification during adolescence: Links to life satisfaction and depressice symptoms</t>
+  </si>
+  <si>
+    <t>Chen &amp; Jackson</t>
+  </si>
+  <si>
+    <t>Predictors of changes in nody image concerns of Chinese adolescents</t>
+  </si>
+  <si>
+    <t>Chen</t>
+  </si>
+  <si>
+    <t>Subjective poverty, deprivation, and the subjective well-being of children and young people: A multilevel growth curve analysis in Taiwan</t>
+  </si>
+  <si>
+    <t>Purpose trajectories during middle adolescence: The role of family, teacher, and peer support</t>
+  </si>
+  <si>
+    <t>Delfabbro et al.</t>
+  </si>
+  <si>
+    <t>Factors associated with attrition in a 10-year longitudinal study of young people: Implications for studies of emplyment in school leavers</t>
+  </si>
+  <si>
+    <t>Dill et al.</t>
+  </si>
+  <si>
+    <t>Negative affect in vicitimized children: The roles of social withdrawal, peer rejection, and attitudes toward bullying</t>
+  </si>
+  <si>
+    <t>Duineveld et al.</t>
+  </si>
+  <si>
+    <t>The link between perceived maternal and paternal autonomy support and adolescent well-being across three major educational transitions</t>
+  </si>
+  <si>
+    <t>Fosco &amp; Feinberg</t>
+  </si>
+  <si>
+    <t>Cascading effects of interparental conflict in adolescence: Limking threat appraisals, self-efficacy, and adjustment</t>
+  </si>
+  <si>
+    <t>Gerber et al.</t>
+  </si>
+  <si>
+    <t>Adolescents with high mental toughness adapt better to perceived stress: A longitudinal study with Swiss vocational students</t>
+  </si>
+  <si>
+    <t>Gillham et al.</t>
+  </si>
+  <si>
+    <t>Character strengths predict subjective well-being during adolescence</t>
+  </si>
+  <si>
+    <t>Haase et al.</t>
+  </si>
+  <si>
+    <t>Happiness as a motivator: Positive affect predicts primary control striving for career and educational goals</t>
+  </si>
+  <si>
+    <t>Haraden et al.</t>
+  </si>
+  <si>
+    <t>Internalizing symptoms and chronotype in youth: A longitudinal assessment of anxiety, depression and tripartite model</t>
+  </si>
+  <si>
+    <t>Trajectories in sense of identity and relationship with life satisfaction during adolescence and young adulthood</t>
+  </si>
+  <si>
+    <t>Jackson &amp; Chen</t>
+  </si>
+  <si>
+    <t>Risk factors for disordered eating during early and middle adolescence: A two year longitudinal study of mainland Chinese boys and girls</t>
+  </si>
+  <si>
+    <t>Cumulative risk and subjective well-being among rural-to-urban migrant adolescents in China: Differential moderating roles of stressmindset and resilience</t>
+  </si>
+  <si>
+    <t>Jose et al.</t>
+  </si>
+  <si>
+    <t>Does social connectedness promote a greater sense of well-being in adolescence over time?</t>
+  </si>
+  <si>
+    <t>Jung &amp; Choi</t>
+  </si>
+  <si>
+    <t>Life satisfaction and delinquent behaviors among Korean adolescents</t>
+  </si>
+  <si>
+    <t>Liem et al.</t>
+  </si>
+  <si>
+    <t>Depressive Symptoms and Life Satisfaction Among Emerging Adults: A Comparison of High School Dropouts and Graduates</t>
+  </si>
+  <si>
+    <t>The Effect of Family Cohesion and Life Satisfaction During Adolescence on Later Adolescent Outcomes:A Prospective Study</t>
+  </si>
+  <si>
+    <t>Marques</t>
+  </si>
+  <si>
+    <t>Psychological Strengths in Childhood as Predictors of Longitudinal Outcomes</t>
+  </si>
+  <si>
+    <t>Martin et al.</t>
+  </si>
+  <si>
+    <t>The Role of Arts Participation in Students’ Academic and Nonacademic Outcomes: A Longitudinal Study of School, Home, and Community Factors</t>
+  </si>
+  <si>
+    <t>Sample recruitment</t>
+  </si>
+  <si>
+    <t>McCabe &amp; Ricciardelli</t>
+  </si>
+  <si>
+    <t>A Prospective Study of ExtremeWeight Change Behaviors Among Adolescent Boys and Girls</t>
+  </si>
+  <si>
+    <t>Extreme Weight Change Behaviours: Are Overweight and Normal Weight Adolescents Different, and Does this Vary Over Time?</t>
+  </si>
+  <si>
+    <t>Miller et al.</t>
+  </si>
+  <si>
+    <t>The role of negative affect in the persistence of nicotine dependence among alternative high school students: A latent growth curve analysis</t>
+  </si>
+  <si>
+    <t>Ricciardelli et al.</t>
+  </si>
+  <si>
+    <t>A Longitudinal Investigation of the Development of Weight and Muscle Concerns Among Preadolescent Boys</t>
+  </si>
+  <si>
+    <t>Richmond et al.</t>
+  </si>
+  <si>
+    <t>Direct Observations of Parenting and Real-time Negative Affect among Adolescent Smokers and Non-Smokers</t>
+  </si>
+  <si>
+    <t>Shoshani et al.</t>
+  </si>
+  <si>
+    <t>Effects of the Maytiv positive psychology school program on early adolescents' well-being, engagement, and achievement</t>
+  </si>
+  <si>
+    <t>Song et al.</t>
+  </si>
+  <si>
+    <t>Pathways Linking Ethnic Discrimination and Drug-Using Peer Affiliation to Underage Drinking Status Among Mexican-Origin Adolescents</t>
+  </si>
+  <si>
+    <t>Su et al.</t>
+  </si>
+  <si>
+    <t>Future Orientation, Social Support, and Psychological Adjustment among Left-behind Children in Rural China: A Longitudinal Study</t>
+  </si>
+  <si>
+    <t>Suldo &amp; Huebner</t>
+  </si>
+  <si>
+    <t>Does Life Satisfaction Moderate the Effects of Stressful Life Events on Psychopathological Behavior During Adolescence?</t>
+  </si>
+  <si>
+    <t>Sun &amp; Shek</t>
+  </si>
+  <si>
+    <t>Longitudinal Influences of Positive Youth Development and Life Satisfaction on Problem Behaviour among Adolescents in Hong Kong</t>
+  </si>
+  <si>
+    <t>Teng et al.</t>
+  </si>
+  <si>
+    <t>Internet gaming disorder and psychosocial well-being: A longitudinal study of older-aged adolescents and emerging adults</t>
+  </si>
+  <si>
+    <t>Valle et al.</t>
+  </si>
+  <si>
+    <t>An analysis of hope as a psychological strength</t>
+  </si>
+  <si>
+    <t>Van Den Eijnden et al.</t>
+  </si>
+  <si>
+    <t>The impact of heavy and disordered use of games and social media on adolescents’ psychological, social, and school functioning</t>
+  </si>
+  <si>
+    <t>Weinstein et al.</t>
+  </si>
+  <si>
+    <t>The Time-Varying Influences of Peer and Family Support on Adolescent Daily Positive and Negative Affect</t>
+  </si>
+  <si>
+    <t>Life Satisfaction Trajectories during Adolescence and the Transition to Young Adulthood: Findings from a Longitudinal Study of Mexican-origin Youth</t>
+  </si>
+  <si>
+    <t>The relations of migrant status and parenting to Chinese adolescents’ adjustment</t>
+  </si>
+  <si>
+    <t>Zhu &amp; Shek</t>
+  </si>
+  <si>
+    <t>Predictive Effect of Positive Youth Development Attributes on Delinquency Among Adolescents in Mainland China</t>
+  </si>
+  <si>
+    <t>Parental factors and adolescent well-being: Associations between developmental trajectories</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -1051,6 +1063,15 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -1332,11 +1353,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:S153"/>
+  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1395,17 +1416,17 @@
         <v>18</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>19</v>
       </c>
-      <c r="B2" t="n">
+      <c r="B2">
         <v>536</v>
       </c>
       <c r="C2" t="s">
         <v>20</v>
       </c>
-      <c r="D2" t="n">
+      <c r="D2">
         <v>2019</v>
       </c>
       <c r="E2" t="s">
@@ -1454,17 +1475,17 @@
         <v>26</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>27</v>
       </c>
-      <c r="B3" t="n">
+      <c r="B3">
         <v>1510</v>
       </c>
       <c r="C3" t="s">
         <v>28</v>
       </c>
-      <c r="D3" t="n">
+      <c r="D3">
         <v>2023</v>
       </c>
       <c r="E3" t="s">
@@ -1513,17 +1534,17 @@
         <v>26</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>27</v>
       </c>
-      <c r="B4" t="n">
+      <c r="B4">
         <v>1572</v>
       </c>
       <c r="C4" t="s">
         <v>31</v>
       </c>
-      <c r="D4" t="n">
+      <c r="D4">
         <v>2020</v>
       </c>
       <c r="E4" t="s">
@@ -1572,17 +1593,17 @@
         <v>34</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>27</v>
       </c>
-      <c r="B5" t="n">
+      <c r="B5">
         <v>1704</v>
       </c>
       <c r="C5" t="s">
         <v>35</v>
       </c>
-      <c r="D5" t="n">
+      <c r="D5">
         <v>2021</v>
       </c>
       <c r="E5" t="s">
@@ -1631,17 +1652,17 @@
         <v>26</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>37</v>
       </c>
-      <c r="B6" t="n">
+      <c r="B6">
         <v>1045</v>
       </c>
       <c r="C6" t="s">
         <v>38</v>
       </c>
-      <c r="D6" t="n">
+      <c r="D6">
         <v>2022</v>
       </c>
       <c r="E6" t="s">
@@ -1690,17 +1711,17 @@
         <v>26</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>37</v>
       </c>
-      <c r="B7" t="n">
+      <c r="B7">
         <v>1102</v>
       </c>
       <c r="C7" t="s">
         <v>40</v>
       </c>
-      <c r="D7" t="n">
+      <c r="D7">
         <v>2020</v>
       </c>
       <c r="E7" t="s">
@@ -1749,17 +1770,17 @@
         <v>34</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>37</v>
       </c>
-      <c r="B8" t="n">
+      <c r="B8">
         <v>1369</v>
       </c>
       <c r="C8" t="s">
         <v>42</v>
       </c>
-      <c r="D8" t="n">
+      <c r="D8">
         <v>2017</v>
       </c>
       <c r="E8" t="s">
@@ -1808,17 +1829,17 @@
         <v>26</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>37</v>
       </c>
-      <c r="B9" t="n">
+      <c r="B9">
         <v>1411</v>
       </c>
       <c r="C9" t="s">
         <v>44</v>
       </c>
-      <c r="D9" t="n">
+      <c r="D9">
         <v>2022</v>
       </c>
       <c r="E9" t="s">
@@ -1867,17 +1888,17 @@
         <v>34</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>46</v>
       </c>
-      <c r="B10" t="n">
+      <c r="B10">
         <v>2257</v>
       </c>
       <c r="C10" t="s">
         <v>47</v>
       </c>
-      <c r="D10" t="n">
+      <c r="D10">
         <v>2022</v>
       </c>
       <c r="E10" t="s">
@@ -1926,17 +1947,17 @@
         <v>34</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>46</v>
       </c>
-      <c r="B11" t="n">
+      <c r="B11">
         <v>2269</v>
       </c>
       <c r="C11" t="s">
         <v>49</v>
       </c>
-      <c r="D11" t="n">
+      <c r="D11">
         <v>2016</v>
       </c>
       <c r="E11" t="s">
@@ -1985,17 +2006,17 @@
         <v>26</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>46</v>
       </c>
-      <c r="B12" t="n">
+      <c r="B12">
         <v>2489</v>
       </c>
       <c r="C12" t="s">
         <v>51</v>
       </c>
-      <c r="D12" t="n">
+      <c r="D12">
         <v>2022</v>
       </c>
       <c r="E12" t="s">
@@ -2044,17 +2065,17 @@
         <v>26</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>46</v>
       </c>
-      <c r="B13" t="n">
+      <c r="B13">
         <v>2623</v>
       </c>
       <c r="C13" t="s">
         <v>53</v>
       </c>
-      <c r="D13" t="n">
+      <c r="D13">
         <v>2022</v>
       </c>
       <c r="E13" t="s">
@@ -2103,17 +2124,17 @@
         <v>26</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>46</v>
       </c>
-      <c r="B14" t="n">
+      <c r="B14">
         <v>2777</v>
       </c>
       <c r="C14" t="s">
         <v>55</v>
       </c>
-      <c r="D14" t="n">
+      <c r="D14">
         <v>2020</v>
       </c>
       <c r="E14" t="s">
@@ -2162,17 +2183,17 @@
         <v>26</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>46</v>
       </c>
-      <c r="B15" t="n">
+      <c r="B15">
         <v>2844</v>
       </c>
       <c r="C15" t="s">
         <v>57</v>
       </c>
-      <c r="D15" t="n">
+      <c r="D15">
         <v>2019</v>
       </c>
       <c r="E15" t="s">
@@ -2221,17 +2242,17 @@
         <v>26</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>46</v>
       </c>
-      <c r="B16" t="n">
+      <c r="B16">
         <v>2845</v>
       </c>
       <c r="C16" t="s">
         <v>57</v>
       </c>
-      <c r="D16" t="n">
+      <c r="D16">
         <v>2021</v>
       </c>
       <c r="E16" t="s">
@@ -2280,17 +2301,17 @@
         <v>26</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>60</v>
       </c>
-      <c r="B17" t="n">
+      <c r="B17">
         <v>3095</v>
       </c>
       <c r="C17" t="s">
         <v>61</v>
       </c>
-      <c r="D17" t="n">
+      <c r="D17">
         <v>2020</v>
       </c>
       <c r="E17" t="s">
@@ -2339,17 +2360,17 @@
         <v>26</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>60</v>
       </c>
-      <c r="B18" t="n">
+      <c r="B18">
         <v>3189</v>
       </c>
       <c r="C18" t="s">
         <v>63</v>
       </c>
-      <c r="D18" t="n">
+      <c r="D18">
         <v>2016</v>
       </c>
       <c r="E18" t="s">
@@ -2398,17 +2419,17 @@
         <v>34</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>60</v>
       </c>
-      <c r="B19" t="n">
+      <c r="B19">
         <v>3259</v>
       </c>
       <c r="C19" t="s">
         <v>65</v>
       </c>
-      <c r="D19" t="n">
+      <c r="D19">
         <v>2020</v>
       </c>
       <c r="E19" t="s">
@@ -2457,17 +2478,17 @@
         <v>26</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>60</v>
       </c>
-      <c r="B20" t="n">
+      <c r="B20">
         <v>3550</v>
       </c>
       <c r="C20" t="s">
         <v>67</v>
       </c>
-      <c r="D20" t="n">
+      <c r="D20">
         <v>2018</v>
       </c>
       <c r="E20" t="s">
@@ -2516,17 +2537,17 @@
         <v>34</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>60</v>
       </c>
-      <c r="B21" t="n">
+      <c r="B21">
         <v>3554</v>
       </c>
       <c r="C21" t="s">
         <v>67</v>
       </c>
-      <c r="D21" t="n">
+      <c r="D21">
         <v>2018</v>
       </c>
       <c r="E21" t="s">
@@ -2575,17 +2596,17 @@
         <v>34</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>60</v>
       </c>
-      <c r="B22" t="n">
+      <c r="B22">
         <v>3559</v>
       </c>
       <c r="C22" t="s">
         <v>70</v>
       </c>
-      <c r="D22" t="n">
+      <c r="D22">
         <v>2022</v>
       </c>
       <c r="E22" t="s">
@@ -2634,17 +2655,17 @@
         <v>34</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>60</v>
       </c>
-      <c r="B23" t="n">
+      <c r="B23">
         <v>3587</v>
       </c>
       <c r="C23" t="s">
         <v>72</v>
       </c>
-      <c r="D23" t="n">
+      <c r="D23">
         <v>2014</v>
       </c>
       <c r="E23" t="s">
@@ -2693,17 +2714,17 @@
         <v>26</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>60</v>
       </c>
-      <c r="B24" t="n">
+      <c r="B24">
         <v>3619</v>
       </c>
       <c r="C24" t="s">
         <v>74</v>
       </c>
-      <c r="D24" t="n">
+      <c r="D24">
         <v>2022</v>
       </c>
       <c r="E24" t="s">
@@ -2752,17 +2773,17 @@
         <v>34</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>60</v>
       </c>
-      <c r="B25" t="n">
+      <c r="B25">
         <v>3700</v>
       </c>
       <c r="C25" t="s">
         <v>76</v>
       </c>
-      <c r="D25" t="n">
+      <c r="D25">
         <v>2021</v>
       </c>
       <c r="E25" t="s">
@@ -2811,17 +2832,17 @@
         <v>26</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>60</v>
       </c>
-      <c r="B26" t="n">
+      <c r="B26">
         <v>3701</v>
       </c>
       <c r="C26" t="s">
         <v>78</v>
       </c>
-      <c r="D26" t="n">
+      <c r="D26">
         <v>2024</v>
       </c>
       <c r="E26" t="s">
@@ -2870,17 +2891,17 @@
         <v>26</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>60</v>
       </c>
-      <c r="B27" t="n">
+      <c r="B27">
         <v>3702</v>
       </c>
       <c r="C27" t="s">
         <v>76</v>
       </c>
-      <c r="D27" t="n">
+      <c r="D27">
         <v>2021</v>
       </c>
       <c r="E27" t="s">
@@ -2929,17 +2950,17 @@
         <v>26</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>60</v>
       </c>
-      <c r="B28" t="n">
+      <c r="B28">
         <v>3766</v>
       </c>
       <c r="C28" t="s">
         <v>81</v>
       </c>
-      <c r="D28" t="n">
+      <c r="D28">
         <v>2023</v>
       </c>
       <c r="E28" t="s">
@@ -2988,17 +3009,17 @@
         <v>26</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>83</v>
       </c>
-      <c r="B29" t="n">
+      <c r="B29">
         <v>4028</v>
       </c>
       <c r="C29" t="s">
         <v>84</v>
       </c>
-      <c r="D29" t="n">
+      <c r="D29">
         <v>2023</v>
       </c>
       <c r="E29" t="s">
@@ -3047,17 +3068,17 @@
         <v>34</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>83</v>
       </c>
-      <c r="B30" t="n">
+      <c r="B30">
         <v>4029</v>
       </c>
       <c r="C30" t="s">
         <v>86</v>
       </c>
-      <c r="D30" t="n">
+      <c r="D30">
         <v>2017</v>
       </c>
       <c r="E30" t="s">
@@ -3106,17 +3127,17 @@
         <v>26</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>83</v>
       </c>
-      <c r="B31" t="n">
+      <c r="B31">
         <v>4452</v>
       </c>
       <c r="C31" t="s">
         <v>88</v>
       </c>
-      <c r="D31" t="n">
+      <c r="D31">
         <v>2000</v>
       </c>
       <c r="E31" t="s">
@@ -3165,17 +3186,17 @@
         <v>26</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>83</v>
       </c>
-      <c r="B32" t="n">
+      <c r="B32">
         <v>4747</v>
       </c>
       <c r="C32" t="s">
         <v>90</v>
       </c>
-      <c r="D32" t="n">
+      <c r="D32">
         <v>2018</v>
       </c>
       <c r="E32" t="s">
@@ -3224,17 +3245,17 @@
         <v>26</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>83</v>
       </c>
-      <c r="B33" t="n">
+      <c r="B33">
         <v>4759</v>
       </c>
       <c r="C33" t="s">
         <v>92</v>
       </c>
-      <c r="D33" t="n">
+      <c r="D33">
         <v>2024</v>
       </c>
       <c r="E33" t="s">
@@ -3283,17 +3304,17 @@
         <v>26</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>83</v>
       </c>
-      <c r="B34" t="n">
+      <c r="B34">
         <v>4898</v>
       </c>
       <c r="C34" t="s">
         <v>94</v>
       </c>
-      <c r="D34" t="n">
+      <c r="D34">
         <v>2014</v>
       </c>
       <c r="E34" t="s">
@@ -3342,17 +3363,17 @@
         <v>26</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>83</v>
       </c>
-      <c r="B35" t="n">
+      <c r="B35">
         <v>4976</v>
       </c>
       <c r="C35" t="s">
         <v>96</v>
       </c>
-      <c r="D35" t="n">
+      <c r="D35">
         <v>2022</v>
       </c>
       <c r="E35" t="s">
@@ -3401,17 +3422,17 @@
         <v>26</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>98</v>
       </c>
-      <c r="B36" t="n">
+      <c r="B36">
         <v>5138</v>
       </c>
       <c r="C36" t="s">
         <v>99</v>
       </c>
-      <c r="D36" t="n">
+      <c r="D36">
         <v>2017</v>
       </c>
       <c r="E36" t="s">
@@ -3460,17 +3481,17 @@
         <v>26</v>
       </c>
     </row>
-    <row r="37">
+    <row r="37" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>98</v>
       </c>
-      <c r="B37" t="n">
+      <c r="B37">
         <v>5147</v>
       </c>
       <c r="C37" t="s">
         <v>101</v>
       </c>
-      <c r="D37" t="n">
+      <c r="D37">
         <v>2020</v>
       </c>
       <c r="E37" t="s">
@@ -3519,17 +3540,17 @@
         <v>26</v>
       </c>
     </row>
-    <row r="38">
+    <row r="38" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>98</v>
       </c>
-      <c r="B38" t="n">
+      <c r="B38">
         <v>5152</v>
       </c>
       <c r="C38" t="s">
         <v>103</v>
       </c>
-      <c r="D38" t="n">
+      <c r="D38">
         <v>2022</v>
       </c>
       <c r="E38" t="s">
@@ -3578,17 +3599,17 @@
         <v>26</v>
       </c>
     </row>
-    <row r="39">
+    <row r="39" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>98</v>
       </c>
-      <c r="B39" t="n">
+      <c r="B39">
         <v>5157</v>
       </c>
       <c r="C39" t="s">
         <v>103</v>
       </c>
-      <c r="D39" t="n">
+      <c r="D39">
         <v>2020</v>
       </c>
       <c r="E39" t="s">
@@ -3637,17 +3658,17 @@
         <v>34</v>
       </c>
     </row>
-    <row r="40">
+    <row r="40" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>98</v>
       </c>
-      <c r="B40" t="n">
+      <c r="B40">
         <v>5166</v>
       </c>
       <c r="C40" t="s">
         <v>106</v>
       </c>
-      <c r="D40" t="n">
+      <c r="D40">
         <v>2023</v>
       </c>
       <c r="E40" t="s">
@@ -3696,17 +3717,17 @@
         <v>26</v>
       </c>
     </row>
-    <row r="41">
+    <row r="41" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>98</v>
       </c>
-      <c r="B41" t="n">
+      <c r="B41">
         <v>5240</v>
       </c>
       <c r="C41" t="s">
         <v>108</v>
       </c>
-      <c r="D41" t="n">
+      <c r="D41">
         <v>2024</v>
       </c>
       <c r="E41" t="s">
@@ -3755,17 +3776,17 @@
         <v>26</v>
       </c>
     </row>
-    <row r="42">
+    <row r="42" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>98</v>
       </c>
-      <c r="B42" t="n">
+      <c r="B42">
         <v>5274</v>
       </c>
       <c r="C42" t="s">
         <v>110</v>
       </c>
-      <c r="D42" t="n">
+      <c r="D42">
         <v>2020</v>
       </c>
       <c r="E42" t="s">
@@ -3814,17 +3835,17 @@
         <v>26</v>
       </c>
     </row>
-    <row r="43">
+    <row r="43" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>98</v>
       </c>
-      <c r="B43" t="n">
+      <c r="B43">
         <v>5281</v>
       </c>
       <c r="C43" t="s">
         <v>112</v>
       </c>
-      <c r="D43" t="n">
+      <c r="D43">
         <v>2023</v>
       </c>
       <c r="E43" t="s">
@@ -3873,17 +3894,17 @@
         <v>26</v>
       </c>
     </row>
-    <row r="44">
+    <row r="44" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>98</v>
       </c>
-      <c r="B44" t="n">
+      <c r="B44">
         <v>5329</v>
       </c>
       <c r="C44" t="s">
         <v>114</v>
       </c>
-      <c r="D44" t="n">
+      <c r="D44">
         <v>2018</v>
       </c>
       <c r="E44" t="s">
@@ -3932,17 +3953,17 @@
         <v>26</v>
       </c>
     </row>
-    <row r="45">
+    <row r="45" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>98</v>
       </c>
-      <c r="B45" t="n">
+      <c r="B45">
         <v>5438</v>
       </c>
       <c r="C45" t="s">
         <v>116</v>
       </c>
-      <c r="D45" t="n">
+      <c r="D45">
         <v>2015</v>
       </c>
       <c r="E45" t="s">
@@ -3991,17 +4012,17 @@
         <v>26</v>
       </c>
     </row>
-    <row r="46">
+    <row r="46" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>98</v>
       </c>
-      <c r="B46" t="n">
+      <c r="B46">
         <v>5499</v>
       </c>
       <c r="C46" t="s">
         <v>118</v>
       </c>
-      <c r="D46" t="n">
+      <c r="D46">
         <v>2023</v>
       </c>
       <c r="E46" t="s">
@@ -4050,17 +4071,17 @@
         <v>26</v>
       </c>
     </row>
-    <row r="47">
+    <row r="47" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>98</v>
       </c>
-      <c r="B47" t="n">
+      <c r="B47">
         <v>5500</v>
       </c>
       <c r="C47" t="s">
         <v>120</v>
       </c>
-      <c r="D47" t="n">
+      <c r="D47">
         <v>2020</v>
       </c>
       <c r="E47" t="s">
@@ -4109,17 +4130,17 @@
         <v>26</v>
       </c>
     </row>
-    <row r="48">
+    <row r="48" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>122</v>
       </c>
-      <c r="B48" t="n">
+      <c r="B48">
         <v>5629</v>
       </c>
       <c r="C48" t="s">
         <v>123</v>
       </c>
-      <c r="D48" t="n">
+      <c r="D48">
         <v>2017</v>
       </c>
       <c r="E48" t="s">
@@ -4168,17 +4189,17 @@
         <v>26</v>
       </c>
     </row>
-    <row r="49">
+    <row r="49" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>122</v>
       </c>
-      <c r="B49" t="n">
+      <c r="B49">
         <v>5662</v>
       </c>
       <c r="C49" t="s">
         <v>125</v>
       </c>
-      <c r="D49" t="n">
+      <c r="D49">
         <v>2023</v>
       </c>
       <c r="E49" t="s">
@@ -4227,17 +4248,17 @@
         <v>34</v>
       </c>
     </row>
-    <row r="50">
+    <row r="50" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>122</v>
       </c>
-      <c r="B50" t="n">
+      <c r="B50">
         <v>5673</v>
       </c>
       <c r="C50" t="s">
         <v>127</v>
       </c>
-      <c r="D50" t="n">
+      <c r="D50">
         <v>2021</v>
       </c>
       <c r="E50" t="s">
@@ -4286,17 +4307,17 @@
         <v>26</v>
       </c>
     </row>
-    <row r="51">
+    <row r="51" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>122</v>
       </c>
-      <c r="B51" t="n">
+      <c r="B51">
         <v>5681</v>
       </c>
       <c r="C51" t="s">
         <v>129</v>
       </c>
-      <c r="D51" t="n">
+      <c r="D51">
         <v>2015</v>
       </c>
       <c r="E51" t="s">
@@ -4345,17 +4366,17 @@
         <v>26</v>
       </c>
     </row>
-    <row r="52">
+    <row r="52" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>122</v>
       </c>
-      <c r="B52" t="n">
+      <c r="B52">
         <v>5733</v>
       </c>
       <c r="C52" t="s">
         <v>131</v>
       </c>
-      <c r="D52" t="n">
+      <c r="D52">
         <v>2022</v>
       </c>
       <c r="E52" t="s">
@@ -4404,17 +4425,17 @@
         <v>26</v>
       </c>
     </row>
-    <row r="53">
+    <row r="53" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>122</v>
       </c>
-      <c r="B53" t="n">
+      <c r="B53">
         <v>5907</v>
       </c>
       <c r="C53" t="s">
         <v>133</v>
       </c>
-      <c r="D53" t="n">
+      <c r="D53">
         <v>2021</v>
       </c>
       <c r="E53" t="s">
@@ -4463,17 +4484,17 @@
         <v>26</v>
       </c>
     </row>
-    <row r="54">
+    <row r="54" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>122</v>
       </c>
-      <c r="B54" t="n">
+      <c r="B54">
         <v>5917</v>
       </c>
       <c r="C54" t="s">
         <v>135</v>
       </c>
-      <c r="D54" t="n">
+      <c r="D54">
         <v>2024</v>
       </c>
       <c r="E54" t="s">
@@ -4522,17 +4543,17 @@
         <v>26</v>
       </c>
     </row>
-    <row r="55">
+    <row r="55" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>122</v>
       </c>
-      <c r="B55" t="n">
+      <c r="B55">
         <v>5924</v>
       </c>
       <c r="C55" t="s">
         <v>135</v>
       </c>
-      <c r="D55" t="n">
+      <c r="D55">
         <v>2023</v>
       </c>
       <c r="E55" t="s">
@@ -4581,17 +4602,17 @@
         <v>26</v>
       </c>
     </row>
-    <row r="56">
+    <row r="56" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>122</v>
       </c>
-      <c r="B56" t="n">
+      <c r="B56">
         <v>5938</v>
       </c>
       <c r="C56" t="s">
         <v>135</v>
       </c>
-      <c r="D56" t="n">
+      <c r="D56">
         <v>2023</v>
       </c>
       <c r="E56" t="s">
@@ -4640,17 +4661,17 @@
         <v>26</v>
       </c>
     </row>
-    <row r="57">
+    <row r="57" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>122</v>
       </c>
-      <c r="B57" t="n">
+      <c r="B57">
         <v>5941</v>
       </c>
       <c r="C57" t="s">
         <v>135</v>
       </c>
-      <c r="D57" t="n">
+      <c r="D57">
         <v>2024</v>
       </c>
       <c r="E57" t="s">
@@ -4699,17 +4720,17 @@
         <v>34</v>
       </c>
     </row>
-    <row r="58">
+    <row r="58" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>122</v>
       </c>
-      <c r="B58" t="n">
+      <c r="B58">
         <v>5988</v>
       </c>
       <c r="C58" t="s">
         <v>140</v>
       </c>
-      <c r="D58" t="n">
+      <c r="D58">
         <v>2020</v>
       </c>
       <c r="E58" t="s">
@@ -4758,17 +4779,17 @@
         <v>26</v>
       </c>
     </row>
-    <row r="59">
+    <row r="59" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>122</v>
       </c>
-      <c r="B59" t="n">
+      <c r="B59">
         <v>5998</v>
       </c>
       <c r="C59" t="s">
         <v>142</v>
       </c>
-      <c r="D59" t="n">
+      <c r="D59">
         <v>2019</v>
       </c>
       <c r="E59" t="s">
@@ -4817,17 +4838,17 @@
         <v>26</v>
       </c>
     </row>
-    <row r="60">
+    <row r="60" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>144</v>
       </c>
-      <c r="B60" t="n">
+      <c r="B60">
         <v>6033</v>
       </c>
       <c r="C60" t="s">
         <v>145</v>
       </c>
-      <c r="D60" t="n">
+      <c r="D60">
         <v>2024</v>
       </c>
       <c r="E60" t="s">
@@ -4876,17 +4897,17 @@
         <v>26</v>
       </c>
     </row>
-    <row r="61">
+    <row r="61" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>144</v>
       </c>
-      <c r="B61" t="n">
+      <c r="B61">
         <v>6086</v>
       </c>
       <c r="C61" t="s">
         <v>147</v>
       </c>
-      <c r="D61" t="n">
+      <c r="D61">
         <v>2023</v>
       </c>
       <c r="E61" t="s">
@@ -4935,17 +4956,17 @@
         <v>26</v>
       </c>
     </row>
-    <row r="62">
+    <row r="62" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>144</v>
       </c>
-      <c r="B62" t="n">
+      <c r="B62">
         <v>6218</v>
       </c>
       <c r="C62" t="s">
         <v>149</v>
       </c>
-      <c r="D62" t="n">
+      <c r="D62">
         <v>2021</v>
       </c>
       <c r="E62" t="s">
@@ -4994,17 +5015,17 @@
         <v>26</v>
       </c>
     </row>
-    <row r="63">
+    <row r="63" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>144</v>
       </c>
-      <c r="B63" t="n">
+      <c r="B63">
         <v>6219</v>
       </c>
       <c r="C63" t="s">
         <v>149</v>
       </c>
-      <c r="D63" t="n">
+      <c r="D63">
         <v>2023</v>
       </c>
       <c r="E63" t="s">
@@ -5053,17 +5074,17 @@
         <v>26</v>
       </c>
     </row>
-    <row r="64">
+    <row r="64" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>144</v>
       </c>
-      <c r="B64" t="n">
+      <c r="B64">
         <v>6272</v>
       </c>
       <c r="C64" t="s">
         <v>152</v>
       </c>
-      <c r="D64" t="n">
+      <c r="D64">
         <v>2021</v>
       </c>
       <c r="E64" t="s">
@@ -5112,17 +5133,17 @@
         <v>26</v>
       </c>
     </row>
-    <row r="65">
+    <row r="65" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>144</v>
       </c>
-      <c r="B65" t="n">
+      <c r="B65">
         <v>6313</v>
       </c>
       <c r="C65" t="s">
         <v>154</v>
       </c>
-      <c r="D65" t="n">
+      <c r="D65">
         <v>2015</v>
       </c>
       <c r="E65" t="s">
@@ -5171,17 +5192,17 @@
         <v>26</v>
       </c>
     </row>
-    <row r="66">
+    <row r="66" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>144</v>
       </c>
-      <c r="B66" t="n">
+      <c r="B66">
         <v>6345</v>
       </c>
       <c r="C66" t="s">
         <v>156</v>
       </c>
-      <c r="D66" t="n">
+      <c r="D66">
         <v>2021</v>
       </c>
       <c r="E66" t="s">
@@ -5230,17 +5251,17 @@
         <v>26</v>
       </c>
     </row>
-    <row r="67">
+    <row r="67" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>144</v>
       </c>
-      <c r="B67" t="n">
+      <c r="B67">
         <v>6346</v>
       </c>
       <c r="C67" t="s">
         <v>156</v>
       </c>
-      <c r="D67" t="n">
+      <c r="D67">
         <v>2023</v>
       </c>
       <c r="E67" t="s">
@@ -5289,17 +5310,17 @@
         <v>26</v>
       </c>
     </row>
-    <row r="68">
+    <row r="68" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>144</v>
       </c>
-      <c r="B68" t="n">
+      <c r="B68">
         <v>6452</v>
       </c>
       <c r="C68" t="s">
         <v>159</v>
       </c>
-      <c r="D68" t="n">
+      <c r="D68">
         <v>2021</v>
       </c>
       <c r="E68" t="s">
@@ -5348,17 +5369,17 @@
         <v>26</v>
       </c>
     </row>
-    <row r="69">
+    <row r="69" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>144</v>
       </c>
-      <c r="B69" t="n">
+      <c r="B69">
         <v>6484</v>
       </c>
       <c r="C69" t="s">
         <v>161</v>
       </c>
-      <c r="D69" t="n">
+      <c r="D69">
         <v>2013</v>
       </c>
       <c r="E69" t="s">
@@ -5407,17 +5428,17 @@
         <v>26</v>
       </c>
     </row>
-    <row r="70">
+    <row r="70" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>144</v>
       </c>
-      <c r="B70" t="n">
+      <c r="B70">
         <v>6485</v>
       </c>
       <c r="C70" t="s">
         <v>161</v>
       </c>
-      <c r="D70" t="n">
+      <c r="D70">
         <v>2011</v>
       </c>
       <c r="E70" t="s">
@@ -5466,17 +5487,17 @@
         <v>26</v>
       </c>
     </row>
-    <row r="71">
+    <row r="71" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>144</v>
       </c>
-      <c r="B71" t="n">
+      <c r="B71">
         <v>6559</v>
       </c>
       <c r="C71" t="s">
         <v>164</v>
       </c>
-      <c r="D71" t="n">
+      <c r="D71">
         <v>2011</v>
       </c>
       <c r="E71" t="s">
@@ -5525,17 +5546,17 @@
         <v>26</v>
       </c>
     </row>
-    <row r="72">
+    <row r="72" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>144</v>
       </c>
-      <c r="B72" t="n">
+      <c r="B72">
         <v>6578</v>
       </c>
       <c r="C72" t="s">
         <v>166</v>
       </c>
-      <c r="D72" t="n">
+      <c r="D72">
         <v>2023</v>
       </c>
       <c r="E72" t="s">
@@ -5584,17 +5605,17 @@
         <v>26</v>
       </c>
     </row>
-    <row r="73">
+    <row r="73" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>144</v>
       </c>
-      <c r="B73" t="n">
+      <c r="B73">
         <v>6774</v>
       </c>
       <c r="C73" t="s">
         <v>168</v>
       </c>
-      <c r="D73" t="n">
+      <c r="D73">
         <v>2016</v>
       </c>
       <c r="E73" t="s">
@@ -5643,17 +5664,17 @@
         <v>26</v>
       </c>
     </row>
-    <row r="74">
+    <row r="74" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>144</v>
       </c>
-      <c r="B74" t="n">
+      <c r="B74">
         <v>6908</v>
       </c>
       <c r="C74" t="s">
         <v>170</v>
       </c>
-      <c r="D74" t="n">
+      <c r="D74">
         <v>2022</v>
       </c>
       <c r="E74" t="s">
@@ -5702,17 +5723,17 @@
         <v>26</v>
       </c>
     </row>
-    <row r="75">
+    <row r="75" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>144</v>
       </c>
-      <c r="B75" t="n">
+      <c r="B75">
         <v>6971</v>
       </c>
       <c r="C75" t="s">
         <v>172</v>
       </c>
-      <c r="D75" t="n">
+      <c r="D75">
         <v>2020</v>
       </c>
       <c r="E75" t="s">
@@ -5761,17 +5782,17 @@
         <v>26</v>
       </c>
     </row>
-    <row r="76">
+    <row r="76" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>174</v>
       </c>
-      <c r="B76" t="n">
+      <c r="B76">
         <v>7412</v>
       </c>
       <c r="C76" t="s">
         <v>175</v>
       </c>
-      <c r="D76" t="n">
+      <c r="D76">
         <v>2023</v>
       </c>
       <c r="E76" t="s">
@@ -5820,17 +5841,17 @@
         <v>26</v>
       </c>
     </row>
-    <row r="77">
+    <row r="77" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>174</v>
       </c>
-      <c r="B77" t="n">
+      <c r="B77">
         <v>7544</v>
       </c>
       <c r="C77" t="s">
         <v>177</v>
       </c>
-      <c r="D77" t="n">
+      <c r="D77">
         <v>2022</v>
       </c>
       <c r="E77" t="s">
@@ -5879,17 +5900,17 @@
         <v>26</v>
       </c>
     </row>
-    <row r="78">
+    <row r="78" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>174</v>
       </c>
-      <c r="B78" t="n">
+      <c r="B78">
         <v>7663</v>
       </c>
       <c r="C78" t="s">
         <v>179</v>
       </c>
-      <c r="D78" t="n">
+      <c r="D78">
         <v>2024</v>
       </c>
       <c r="E78" t="s">
@@ -5938,17 +5959,17 @@
         <v>26</v>
       </c>
     </row>
-    <row r="79">
+    <row r="79" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>174</v>
       </c>
-      <c r="B79" t="n">
+      <c r="B79">
         <v>7804</v>
       </c>
       <c r="C79" t="s">
         <v>181</v>
       </c>
-      <c r="D79" t="n">
+      <c r="D79">
         <v>2008</v>
       </c>
       <c r="E79" t="s">
@@ -5997,17 +6018,17 @@
         <v>26</v>
       </c>
     </row>
-    <row r="80">
+    <row r="80" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>174</v>
       </c>
-      <c r="B80" t="n">
+      <c r="B80">
         <v>7836</v>
       </c>
       <c r="C80" t="s">
         <v>183</v>
       </c>
-      <c r="D80" t="n">
+      <c r="D80">
         <v>2022</v>
       </c>
       <c r="E80" t="s">
@@ -6056,17 +6077,17 @@
         <v>26</v>
       </c>
     </row>
-    <row r="81">
+    <row r="81" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>174</v>
       </c>
-      <c r="B81" t="n">
+      <c r="B81">
         <v>7866</v>
       </c>
       <c r="C81" t="s">
         <v>185</v>
       </c>
-      <c r="D81" t="n">
+      <c r="D81">
         <v>2015</v>
       </c>
       <c r="E81" t="s">
@@ -6115,17 +6136,17 @@
         <v>26</v>
       </c>
     </row>
-    <row r="82">
+    <row r="82" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>187</v>
       </c>
-      <c r="B82" t="n">
+      <c r="B82">
         <v>8145</v>
       </c>
       <c r="C82" t="s">
         <v>188</v>
       </c>
-      <c r="D82" t="n">
+      <c r="D82">
         <v>2021</v>
       </c>
       <c r="E82" t="s">
@@ -6174,17 +6195,17 @@
         <v>26</v>
       </c>
     </row>
-    <row r="83">
+    <row r="83" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>187</v>
       </c>
-      <c r="B83" t="n">
+      <c r="B83">
         <v>8202</v>
       </c>
       <c r="C83" t="s">
         <v>190</v>
       </c>
-      <c r="D83" t="n">
+      <c r="D83">
         <v>2021</v>
       </c>
       <c r="E83" t="s">
@@ -6233,17 +6254,17 @@
         <v>26</v>
       </c>
     </row>
-    <row r="84">
+    <row r="84" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>187</v>
       </c>
-      <c r="B84" t="n">
+      <c r="B84">
         <v>8834</v>
       </c>
       <c r="C84" t="s">
         <v>192</v>
       </c>
-      <c r="D84" t="n">
+      <c r="D84">
         <v>2010</v>
       </c>
       <c r="E84" t="s">
@@ -6292,17 +6313,17 @@
         <v>26</v>
       </c>
     </row>
-    <row r="85">
+    <row r="85" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>187</v>
       </c>
-      <c r="B85" t="n">
+      <c r="B85">
         <v>8875</v>
       </c>
       <c r="C85" t="s">
         <v>194</v>
       </c>
-      <c r="D85" t="n">
+      <c r="D85">
         <v>2010</v>
       </c>
       <c r="E85" t="s">
@@ -6351,17 +6372,17 @@
         <v>26</v>
       </c>
     </row>
-    <row r="86">
+    <row r="86" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>187</v>
       </c>
-      <c r="B86" t="n">
+      <c r="B86">
         <v>8876</v>
       </c>
       <c r="C86" t="s">
         <v>196</v>
       </c>
-      <c r="D86" t="n">
+      <c r="D86">
         <v>2010</v>
       </c>
       <c r="E86" t="s">
@@ -6410,17 +6431,17 @@
         <v>26</v>
       </c>
     </row>
-    <row r="87">
+    <row r="87" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>187</v>
       </c>
-      <c r="B87" t="n">
+      <c r="B87">
         <v>8880</v>
       </c>
       <c r="C87" t="s">
         <v>198</v>
       </c>
-      <c r="D87" t="n">
+      <c r="D87">
         <v>2008</v>
       </c>
       <c r="E87" t="s">
@@ -6469,17 +6490,17 @@
         <v>26</v>
       </c>
     </row>
-    <row r="88">
+    <row r="88" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>187</v>
       </c>
-      <c r="B88" t="n">
+      <c r="B88">
         <v>8903</v>
       </c>
       <c r="C88" t="s">
         <v>200</v>
       </c>
-      <c r="D88" t="n">
+      <c r="D88">
         <v>2015</v>
       </c>
       <c r="E88" t="s">
@@ -6528,17 +6549,17 @@
         <v>26</v>
       </c>
     </row>
-    <row r="89">
+    <row r="89" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>187</v>
       </c>
-      <c r="B89" t="n">
+      <c r="B89">
         <v>8904</v>
       </c>
       <c r="C89" t="s">
         <v>202</v>
       </c>
-      <c r="D89" t="n">
+      <c r="D89">
         <v>2019</v>
       </c>
       <c r="E89" t="s">
@@ -6587,17 +6608,17 @@
         <v>26</v>
       </c>
     </row>
-    <row r="90">
+    <row r="90" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>204</v>
       </c>
-      <c r="B90" t="n">
+      <c r="B90">
         <v>9112</v>
       </c>
       <c r="C90" t="s">
         <v>205</v>
       </c>
-      <c r="D90" t="n">
+      <c r="D90">
         <v>2006</v>
       </c>
       <c r="E90" t="s">
@@ -6646,17 +6667,17 @@
         <v>26</v>
       </c>
     </row>
-    <row r="91">
+    <row r="91" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>204</v>
       </c>
-      <c r="B91" t="n">
+      <c r="B91">
         <v>9235</v>
       </c>
       <c r="C91" t="s">
         <v>207</v>
       </c>
-      <c r="D91" t="n">
+      <c r="D91">
         <v>2007</v>
       </c>
       <c r="E91" t="s">
@@ -6705,17 +6726,17 @@
         <v>26</v>
       </c>
     </row>
-    <row r="92">
+    <row r="92" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>204</v>
       </c>
-      <c r="B92" t="n">
+      <c r="B92">
         <v>9243</v>
       </c>
       <c r="C92" t="s">
         <v>209</v>
       </c>
-      <c r="D92" t="n">
+      <c r="D92">
         <v>2016</v>
       </c>
       <c r="E92" t="s">
@@ -6764,17 +6785,17 @@
         <v>26</v>
       </c>
     </row>
-    <row r="93">
+    <row r="93" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>204</v>
       </c>
-      <c r="B93" t="n">
+      <c r="B93">
         <v>9248</v>
       </c>
       <c r="C93" t="s">
         <v>211</v>
       </c>
-      <c r="D93" t="n">
+      <c r="D93">
         <v>2014</v>
       </c>
       <c r="E93" t="s">
@@ -6823,17 +6844,17 @@
         <v>26</v>
       </c>
     </row>
-    <row r="94">
+    <row r="94" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>204</v>
       </c>
-      <c r="B94" t="n">
+      <c r="B94">
         <v>9285</v>
       </c>
       <c r="C94" t="s">
         <v>213</v>
       </c>
-      <c r="D94" t="n">
+      <c r="D94">
         <v>2023</v>
       </c>
       <c r="E94" t="s">
@@ -6882,17 +6903,17 @@
         <v>26</v>
       </c>
     </row>
-    <row r="95">
+    <row r="95" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>204</v>
       </c>
-      <c r="B95" t="n">
+      <c r="B95">
         <v>9333</v>
       </c>
       <c r="C95" t="s">
         <v>215</v>
       </c>
-      <c r="D95" t="n">
+      <c r="D95">
         <v>2013</v>
       </c>
       <c r="E95" t="s">
@@ -6941,17 +6962,17 @@
         <v>26</v>
       </c>
     </row>
-    <row r="96">
+    <row r="96" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>204</v>
       </c>
-      <c r="B96" t="n">
+      <c r="B96">
         <v>9603</v>
       </c>
       <c r="C96" t="s">
         <v>217</v>
       </c>
-      <c r="D96" t="n">
+      <c r="D96">
         <v>2019</v>
       </c>
       <c r="E96" t="s">
@@ -7000,17 +7021,17 @@
         <v>26</v>
       </c>
     </row>
-    <row r="97">
+    <row r="97" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>204</v>
       </c>
-      <c r="B97" t="n">
+      <c r="B97">
         <v>9693</v>
       </c>
       <c r="C97" t="s">
         <v>219</v>
       </c>
-      <c r="D97" t="n">
+      <c r="D97">
         <v>2019</v>
       </c>
       <c r="E97" t="s">
@@ -7059,17 +7080,17 @@
         <v>26</v>
       </c>
     </row>
-    <row r="98">
+    <row r="98" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>204</v>
       </c>
-      <c r="B98" t="n">
+      <c r="B98">
         <v>9724</v>
       </c>
       <c r="C98" t="s">
         <v>222</v>
       </c>
-      <c r="D98" t="n">
+      <c r="D98">
         <v>2023</v>
       </c>
       <c r="E98" t="s">
@@ -7118,17 +7139,17 @@
         <v>26</v>
       </c>
     </row>
-    <row r="99">
+    <row r="99" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>224</v>
       </c>
-      <c r="B99" t="n">
+      <c r="B99">
         <v>10118</v>
       </c>
       <c r="C99" t="s">
         <v>225</v>
       </c>
-      <c r="D99" t="n">
+      <c r="D99">
         <v>2015</v>
       </c>
       <c r="E99" t="s">
@@ -7177,17 +7198,17 @@
         <v>26</v>
       </c>
     </row>
-    <row r="100">
+    <row r="100" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>224</v>
       </c>
-      <c r="B100" t="n">
+      <c r="B100">
         <v>10300</v>
       </c>
       <c r="C100" t="s">
         <v>227</v>
       </c>
-      <c r="D100" t="n">
+      <c r="D100">
         <v>2020</v>
       </c>
       <c r="E100" t="s">
@@ -7236,17 +7257,17 @@
         <v>26</v>
       </c>
     </row>
-    <row r="101">
+    <row r="101" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>224</v>
       </c>
-      <c r="B101" t="n">
+      <c r="B101">
         <v>10440</v>
       </c>
       <c r="C101" t="s">
         <v>229</v>
       </c>
-      <c r="D101" t="n">
+      <c r="D101">
         <v>2021</v>
       </c>
       <c r="E101" t="s">
@@ -7295,17 +7316,17 @@
         <v>26</v>
       </c>
     </row>
-    <row r="102">
+    <row r="102" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>224</v>
       </c>
-      <c r="B102" t="n">
+      <c r="B102">
         <v>10792</v>
       </c>
       <c r="C102" t="s">
         <v>231</v>
       </c>
-      <c r="D102" t="n">
+      <c r="D102">
         <v>2023</v>
       </c>
       <c r="E102" t="s">
@@ -7354,17 +7375,17 @@
         <v>26</v>
       </c>
     </row>
-    <row r="103">
+    <row r="103" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>224</v>
       </c>
-      <c r="B103" t="n">
+      <c r="B103">
         <v>10860</v>
       </c>
       <c r="C103" t="s">
         <v>233</v>
       </c>
-      <c r="D103" t="n">
+      <c r="D103">
         <v>2021</v>
       </c>
       <c r="E103" t="s">
@@ -7413,17 +7434,17 @@
         <v>26</v>
       </c>
     </row>
-    <row r="104">
+    <row r="104" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>224</v>
       </c>
-      <c r="B104" t="n">
+      <c r="B104">
         <v>10994</v>
       </c>
       <c r="C104" t="s">
         <v>235</v>
       </c>
-      <c r="D104" t="n">
+      <c r="D104">
         <v>2023</v>
       </c>
       <c r="E104" t="s">
@@ -7472,17 +7493,17 @@
         <v>26</v>
       </c>
     </row>
-    <row r="105">
+    <row r="105" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
         <v>224</v>
       </c>
-      <c r="B105" t="n">
+      <c r="B105">
         <v>11046</v>
       </c>
       <c r="C105" t="s">
         <v>239</v>
       </c>
-      <c r="D105" t="n">
+      <c r="D105">
         <v>2021</v>
       </c>
       <c r="E105" t="s">
@@ -7531,17 +7552,17 @@
         <v>26</v>
       </c>
     </row>
-    <row r="106">
+    <row r="106" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>241</v>
       </c>
-      <c r="B106" t="n">
+      <c r="B106">
         <v>11191</v>
       </c>
       <c r="C106" t="s">
         <v>242</v>
       </c>
-      <c r="D106" t="n">
+      <c r="D106">
         <v>2023</v>
       </c>
       <c r="E106" t="s">
@@ -7590,17 +7611,17 @@
         <v>26</v>
       </c>
     </row>
-    <row r="107">
+    <row r="107" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>241</v>
       </c>
-      <c r="B107" t="n">
+      <c r="B107">
         <v>11206</v>
       </c>
       <c r="C107" t="s">
         <v>244</v>
       </c>
-      <c r="D107" t="n">
+      <c r="D107">
         <v>2023</v>
       </c>
       <c r="E107" t="s">
@@ -7649,17 +7670,17 @@
         <v>26</v>
       </c>
     </row>
-    <row r="108">
+    <row r="108" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>241</v>
       </c>
-      <c r="B108" t="n">
+      <c r="B108">
         <v>11234</v>
       </c>
       <c r="C108" t="s">
         <v>246</v>
       </c>
-      <c r="D108" t="n">
+      <c r="D108">
         <v>2023</v>
       </c>
       <c r="E108" t="s">
@@ -7708,17 +7729,17 @@
         <v>26</v>
       </c>
     </row>
-    <row r="109">
+    <row r="109" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>241</v>
       </c>
-      <c r="B109" t="n">
+      <c r="B109">
         <v>11522</v>
       </c>
       <c r="C109" t="s">
         <v>248</v>
       </c>
-      <c r="D109" t="n">
+      <c r="D109">
         <v>2016</v>
       </c>
       <c r="E109" t="s">
@@ -7767,17 +7788,17 @@
         <v>26</v>
       </c>
     </row>
-    <row r="110">
+    <row r="110" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
         <v>250</v>
       </c>
-      <c r="B110" t="n">
+      <c r="B110">
         <v>11523</v>
       </c>
       <c r="C110" t="s">
         <v>251</v>
       </c>
-      <c r="D110" t="n">
+      <c r="D110">
         <v>2010</v>
       </c>
       <c r="E110" t="s">
@@ -7826,17 +7847,17 @@
         <v>26</v>
       </c>
     </row>
-    <row r="111">
+    <row r="111" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
         <v>250</v>
       </c>
-      <c r="B111" t="n">
+      <c r="B111">
         <v>11524</v>
       </c>
       <c r="C111" t="s">
         <v>253</v>
       </c>
-      <c r="D111" t="n">
+      <c r="D111">
         <v>2014</v>
       </c>
       <c r="E111" t="s">
@@ -7885,17 +7906,17 @@
         <v>34</v>
       </c>
     </row>
-    <row r="112">
+    <row r="112" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
         <v>250</v>
       </c>
-      <c r="B112" t="n">
+      <c r="B112">
         <v>11526</v>
       </c>
       <c r="C112" t="s">
         <v>255</v>
       </c>
-      <c r="D112" t="n">
+      <c r="D112">
         <v>2006</v>
       </c>
       <c r="E112" t="s">
@@ -7944,17 +7965,17 @@
         <v>26</v>
       </c>
     </row>
-    <row r="113">
+    <row r="113" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
         <v>250</v>
       </c>
-      <c r="B113" t="n">
+      <c r="B113">
         <v>11527</v>
       </c>
       <c r="C113" t="s">
         <v>257</v>
       </c>
-      <c r="D113" t="n">
+      <c r="D113">
         <v>2023</v>
       </c>
       <c r="E113" t="s">
@@ -8003,17 +8024,17 @@
         <v>26</v>
       </c>
     </row>
-    <row r="114">
+    <row r="114" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
         <v>250</v>
       </c>
-      <c r="B114" t="n">
+      <c r="B114">
         <v>11529</v>
       </c>
       <c r="C114" t="s">
         <v>259</v>
       </c>
-      <c r="D114" t="n">
+      <c r="D114">
         <v>2017</v>
       </c>
       <c r="E114" t="s">
@@ -8062,17 +8083,17 @@
         <v>26</v>
       </c>
     </row>
-    <row r="115">
+    <row r="115" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
         <v>250</v>
       </c>
-      <c r="B115" t="n">
+      <c r="B115">
         <v>11531</v>
       </c>
       <c r="C115" t="s">
         <v>261</v>
       </c>
-      <c r="D115" t="n">
+      <c r="D115">
         <v>2020</v>
       </c>
       <c r="E115" t="s">
@@ -8121,17 +8142,17 @@
         <v>26</v>
       </c>
     </row>
-    <row r="116">
+    <row r="116" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
         <v>250</v>
       </c>
-      <c r="B116" t="n">
+      <c r="B116">
         <v>11532</v>
       </c>
       <c r="C116" t="s">
         <v>263</v>
       </c>
-      <c r="D116" t="n">
+      <c r="D116">
         <v>2009</v>
       </c>
       <c r="E116" t="s">
@@ -8180,17 +8201,17 @@
         <v>26</v>
       </c>
     </row>
-    <row r="117">
+    <row r="117" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
         <v>250</v>
       </c>
-      <c r="B117" t="n">
+      <c r="B117">
         <v>11533</v>
       </c>
       <c r="C117" t="s">
         <v>265</v>
       </c>
-      <c r="D117" t="n">
+      <c r="D117">
         <v>2020</v>
       </c>
       <c r="E117" t="s">
@@ -8239,17 +8260,17 @@
         <v>26</v>
       </c>
     </row>
-    <row r="118">
+    <row r="118" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
         <v>250</v>
       </c>
-      <c r="B118" t="n">
+      <c r="B118">
         <v>11534</v>
       </c>
       <c r="C118" t="s">
         <v>35</v>
       </c>
-      <c r="D118" t="n">
+      <c r="D118">
         <v>2022</v>
       </c>
       <c r="E118" t="s">
@@ -8298,17 +8319,17 @@
         <v>26</v>
       </c>
     </row>
-    <row r="119">
+    <row r="119" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
         <v>250</v>
       </c>
-      <c r="B119" t="n">
+      <c r="B119">
         <v>11536</v>
       </c>
       <c r="C119" t="s">
         <v>268</v>
       </c>
-      <c r="D119" t="n">
+      <c r="D119">
         <v>2017</v>
       </c>
       <c r="E119" t="s">
@@ -8357,17 +8378,17 @@
         <v>26</v>
       </c>
     </row>
-    <row r="120">
+    <row r="120" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
         <v>250</v>
       </c>
-      <c r="B120" t="n">
+      <c r="B120">
         <v>11537</v>
       </c>
       <c r="C120" t="s">
         <v>270</v>
       </c>
-      <c r="D120" t="n">
+      <c r="D120">
         <v>2004</v>
       </c>
       <c r="E120" t="s">
@@ -8416,17 +8437,17 @@
         <v>26</v>
       </c>
     </row>
-    <row r="121">
+    <row r="121" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
         <v>250</v>
       </c>
-      <c r="B121" t="n">
+      <c r="B121">
         <v>11539</v>
       </c>
       <c r="C121" t="s">
         <v>272</v>
       </c>
-      <c r="D121" t="n">
+      <c r="D121">
         <v>2017</v>
       </c>
       <c r="E121" t="s">
@@ -8475,17 +8496,17 @@
         <v>26</v>
       </c>
     </row>
-    <row r="122">
+    <row r="122" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
         <v>250</v>
       </c>
-      <c r="B122" t="n">
+      <c r="B122">
         <v>11541</v>
       </c>
       <c r="C122" t="s">
         <v>274</v>
       </c>
-      <c r="D122" t="n">
+      <c r="D122">
         <v>2015</v>
       </c>
       <c r="E122" t="s">
@@ -8534,17 +8555,17 @@
         <v>26</v>
       </c>
     </row>
-    <row r="123">
+    <row r="123" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
         <v>250</v>
       </c>
-      <c r="B123" t="n">
+      <c r="B123">
         <v>11543</v>
       </c>
       <c r="C123" t="s">
         <v>276</v>
       </c>
-      <c r="D123" t="n">
+      <c r="D123">
         <v>2013</v>
       </c>
       <c r="E123" t="s">
@@ -8593,17 +8614,17 @@
         <v>26</v>
       </c>
     </row>
-    <row r="124">
+    <row r="124" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
         <v>250</v>
       </c>
-      <c r="B124" t="n">
+      <c r="B124">
         <v>11544</v>
       </c>
       <c r="C124" t="s">
         <v>278</v>
       </c>
-      <c r="D124" t="n">
+      <c r="D124">
         <v>2011</v>
       </c>
       <c r="E124" t="s">
@@ -8652,17 +8673,17 @@
         <v>26</v>
       </c>
     </row>
-    <row r="125">
+    <row r="125" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
         <v>250</v>
       </c>
-      <c r="B125" t="n">
+      <c r="B125">
         <v>11545</v>
       </c>
       <c r="C125" t="s">
         <v>280</v>
       </c>
-      <c r="D125" t="n">
+      <c r="D125">
         <v>2012</v>
       </c>
       <c r="E125" t="s">
@@ -8711,17 +8732,17 @@
         <v>26</v>
       </c>
     </row>
-    <row r="126">
+    <row r="126" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
         <v>250</v>
       </c>
-      <c r="B126" t="n">
+      <c r="B126">
         <v>11547</v>
       </c>
       <c r="C126" t="s">
         <v>282</v>
       </c>
-      <c r="D126" t="n">
+      <c r="D126">
         <v>2019</v>
       </c>
       <c r="E126" t="s">
@@ -8770,17 +8791,17 @@
         <v>26</v>
       </c>
     </row>
-    <row r="127">
+    <row r="127" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
         <v>250</v>
       </c>
-      <c r="B127" t="n">
+      <c r="B127">
         <v>11548</v>
       </c>
       <c r="C127" t="s">
         <v>84</v>
       </c>
-      <c r="D127" t="n">
+      <c r="D127">
         <v>2022</v>
       </c>
       <c r="E127" t="s">
@@ -8829,17 +8850,17 @@
         <v>26</v>
       </c>
     </row>
-    <row r="128">
+    <row r="128" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
         <v>250</v>
       </c>
-      <c r="B128" t="n">
+      <c r="B128">
         <v>11551</v>
       </c>
       <c r="C128" t="s">
         <v>285</v>
       </c>
-      <c r="D128" t="n">
+      <c r="D128">
         <v>2014</v>
       </c>
       <c r="E128" t="s">
@@ -8888,17 +8909,17 @@
         <v>26</v>
       </c>
     </row>
-    <row r="129">
+    <row r="129" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
         <v>250</v>
       </c>
-      <c r="B129" t="n">
+      <c r="B129">
         <v>11552</v>
       </c>
       <c r="C129" t="s">
         <v>92</v>
       </c>
-      <c r="D129" t="n">
+      <c r="D129">
         <v>2020</v>
       </c>
       <c r="E129" t="s">
@@ -8947,17 +8968,17 @@
         <v>26</v>
       </c>
     </row>
-    <row r="130">
+    <row r="130" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
         <v>250</v>
       </c>
-      <c r="B130" t="n">
+      <c r="B130">
         <v>11553</v>
       </c>
       <c r="C130" t="s">
         <v>288</v>
       </c>
-      <c r="D130" t="n">
+      <c r="D130">
         <v>2012</v>
       </c>
       <c r="E130" t="s">
@@ -9006,17 +9027,17 @@
         <v>26</v>
       </c>
     </row>
-    <row r="131">
+    <row r="131" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
         <v>250</v>
       </c>
-      <c r="B131" t="n">
+      <c r="B131">
         <v>11554</v>
       </c>
       <c r="C131" t="s">
         <v>290</v>
       </c>
-      <c r="D131" t="n">
+      <c r="D131">
         <v>2017</v>
       </c>
       <c r="E131" t="s">
@@ -9065,17 +9086,17 @@
         <v>26</v>
       </c>
     </row>
-    <row r="132">
+    <row r="132" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
         <v>250</v>
       </c>
-      <c r="B132" t="n">
+      <c r="B132">
         <v>11560</v>
       </c>
       <c r="C132" t="s">
         <v>292</v>
       </c>
-      <c r="D132" t="n">
+      <c r="D132">
         <v>2010</v>
       </c>
       <c r="E132" t="s">
@@ -9124,17 +9145,17 @@
         <v>26</v>
       </c>
     </row>
-    <row r="133">
+    <row r="133" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
         <v>250</v>
       </c>
-      <c r="B133" t="n">
+      <c r="B133">
         <v>11562</v>
       </c>
       <c r="C133" t="s">
         <v>142</v>
       </c>
-      <c r="D133" t="n">
+      <c r="D133">
         <v>2019</v>
       </c>
       <c r="E133" t="s">
@@ -9183,17 +9204,17 @@
         <v>26</v>
       </c>
     </row>
-    <row r="134">
+    <row r="134" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
         <v>250</v>
       </c>
-      <c r="B134" t="n">
+      <c r="B134">
         <v>11564</v>
       </c>
       <c r="C134" t="s">
         <v>295</v>
       </c>
-      <c r="D134" t="n">
+      <c r="D134">
         <v>2016</v>
       </c>
       <c r="E134" t="s">
@@ -9242,17 +9263,17 @@
         <v>26</v>
       </c>
     </row>
-    <row r="135">
+    <row r="135" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
         <v>250</v>
       </c>
-      <c r="B135" t="n">
+      <c r="B135">
         <v>11565</v>
       </c>
       <c r="C135" t="s">
         <v>297</v>
       </c>
-      <c r="D135" t="n">
+      <c r="D135">
         <v>2013</v>
       </c>
       <c r="E135" t="s">
@@ -9301,17 +9322,17 @@
         <v>26</v>
       </c>
     </row>
-    <row r="136">
+    <row r="136" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
         <v>250</v>
       </c>
-      <c r="B136" t="n">
+      <c r="B136">
         <v>11566</v>
       </c>
       <c r="C136" t="s">
         <v>300</v>
       </c>
-      <c r="D136" t="n">
+      <c r="D136">
         <v>11566</v>
       </c>
       <c r="E136" t="s">
@@ -9360,17 +9381,17 @@
         <v>26</v>
       </c>
     </row>
-    <row r="137">
+    <row r="137" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
         <v>250</v>
       </c>
-      <c r="B137" t="n">
+      <c r="B137">
         <v>11567</v>
       </c>
       <c r="C137" t="s">
         <v>300</v>
       </c>
-      <c r="D137" t="n">
+      <c r="D137">
         <v>2009</v>
       </c>
       <c r="E137" t="s">
@@ -9419,17 +9440,17 @@
         <v>26</v>
       </c>
     </row>
-    <row r="138">
+    <row r="138" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
         <v>250</v>
       </c>
-      <c r="B138" t="n">
+      <c r="B138">
         <v>11568</v>
       </c>
       <c r="C138" t="s">
         <v>303</v>
       </c>
-      <c r="D138" t="n">
+      <c r="D138">
         <v>2020</v>
       </c>
       <c r="E138" t="s">
@@ -9478,17 +9499,17 @@
         <v>26</v>
       </c>
     </row>
-    <row r="139">
+    <row r="139" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
         <v>250</v>
       </c>
-      <c r="B139" t="n">
+      <c r="B139">
         <v>11573</v>
       </c>
       <c r="C139" t="s">
         <v>305</v>
       </c>
-      <c r="D139" t="n">
+      <c r="D139">
         <v>2006</v>
       </c>
       <c r="E139" t="s">
@@ -9537,17 +9558,17 @@
         <v>26</v>
       </c>
     </row>
-    <row r="140">
+    <row r="140" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
         <v>250</v>
       </c>
-      <c r="B140" t="n">
+      <c r="B140">
         <v>11574</v>
       </c>
       <c r="C140" t="s">
         <v>307</v>
       </c>
-      <c r="D140" t="n">
+      <c r="D140">
         <v>2013</v>
       </c>
       <c r="E140" t="s">
@@ -9596,17 +9617,17 @@
         <v>26</v>
       </c>
     </row>
-    <row r="141">
+    <row r="141" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
         <v>250</v>
       </c>
-      <c r="B141" t="n">
+      <c r="B141">
         <v>11576</v>
       </c>
       <c r="C141" t="s">
         <v>309</v>
       </c>
-      <c r="D141" t="n">
+      <c r="D141">
         <v>2016</v>
       </c>
       <c r="E141" t="s">
@@ -9655,17 +9676,17 @@
         <v>26</v>
       </c>
     </row>
-    <row r="142">
+    <row r="142" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
         <v>250</v>
       </c>
-      <c r="B142" t="n">
+      <c r="B142">
         <v>11577</v>
       </c>
       <c r="C142" t="s">
         <v>311</v>
       </c>
-      <c r="D142" t="n">
+      <c r="D142">
         <v>2022</v>
       </c>
       <c r="E142" t="s">
@@ -9714,17 +9735,17 @@
         <v>26</v>
       </c>
     </row>
-    <row r="143">
+    <row r="143" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
         <v>250</v>
       </c>
-      <c r="B143" t="n">
+      <c r="B143">
         <v>11578</v>
       </c>
       <c r="C143" t="s">
         <v>313</v>
       </c>
-      <c r="D143" t="n">
+      <c r="D143">
         <v>2017</v>
       </c>
       <c r="E143" t="s">
@@ -9773,17 +9794,17 @@
         <v>26</v>
       </c>
     </row>
-    <row r="144">
+    <row r="144" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
         <v>250</v>
       </c>
-      <c r="B144" t="n">
+      <c r="B144">
         <v>11579</v>
       </c>
       <c r="C144" t="s">
         <v>315</v>
       </c>
-      <c r="D144" t="n">
+      <c r="D144">
         <v>2004</v>
       </c>
       <c r="E144" t="s">
@@ -9832,17 +9853,17 @@
         <v>26</v>
       </c>
     </row>
-    <row r="145">
+    <row r="145" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
         <v>250</v>
       </c>
-      <c r="B145" t="n">
+      <c r="B145">
         <v>11580</v>
       </c>
       <c r="C145" t="s">
         <v>317</v>
       </c>
-      <c r="D145" t="n">
+      <c r="D145">
         <v>2013</v>
       </c>
       <c r="E145" t="s">
@@ -9891,17 +9912,17 @@
         <v>26</v>
       </c>
     </row>
-    <row r="146">
+    <row r="146" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
         <v>250</v>
       </c>
-      <c r="B146" t="n">
+      <c r="B146">
         <v>11582</v>
       </c>
       <c r="C146" t="s">
         <v>319</v>
       </c>
-      <c r="D146" t="n">
+      <c r="D146">
         <v>2020</v>
       </c>
       <c r="E146" t="s">
@@ -9950,17 +9971,17 @@
         <v>26</v>
       </c>
     </row>
-    <row r="147">
+    <row r="147" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
         <v>250</v>
       </c>
-      <c r="B147" t="n">
+      <c r="B147">
         <v>11583</v>
       </c>
       <c r="C147" t="s">
         <v>321</v>
       </c>
-      <c r="D147" t="n">
+      <c r="D147">
         <v>2006</v>
       </c>
       <c r="E147" t="s">
@@ -10009,17 +10030,17 @@
         <v>26</v>
       </c>
     </row>
-    <row r="148">
+    <row r="148" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
         <v>250</v>
       </c>
-      <c r="B148" t="n">
+      <c r="B148">
         <v>11584</v>
       </c>
       <c r="C148" t="s">
         <v>323</v>
       </c>
-      <c r="D148" t="n">
+      <c r="D148">
         <v>2018</v>
       </c>
       <c r="E148" t="s">
@@ -10068,17 +10089,17 @@
         <v>26</v>
       </c>
     </row>
-    <row r="149">
+    <row r="149" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
         <v>250</v>
       </c>
-      <c r="B149" t="n">
+      <c r="B149">
         <v>11586</v>
       </c>
       <c r="C149" t="s">
         <v>325</v>
       </c>
-      <c r="D149" t="n">
+      <c r="D149">
         <v>2006</v>
       </c>
       <c r="E149" t="s">
@@ -10127,17 +10148,17 @@
         <v>26</v>
       </c>
     </row>
-    <row r="150">
+    <row r="150" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
         <v>250</v>
       </c>
-      <c r="B150" t="n">
+      <c r="B150">
         <v>11588</v>
       </c>
       <c r="C150" t="s">
         <v>239</v>
       </c>
-      <c r="D150" t="n">
+      <c r="D150">
         <v>2021</v>
       </c>
       <c r="E150" t="s">
@@ -10186,17 +10207,17 @@
         <v>26</v>
       </c>
     </row>
-    <row r="151">
+    <row r="151" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
         <v>250</v>
       </c>
-      <c r="B151" t="n">
+      <c r="B151">
         <v>11591</v>
       </c>
       <c r="C151" t="s">
         <v>248</v>
       </c>
-      <c r="D151" t="n">
+      <c r="D151">
         <v>2017</v>
       </c>
       <c r="E151" t="s">
@@ -10245,17 +10266,17 @@
         <v>26</v>
       </c>
     </row>
-    <row r="152">
+    <row r="152" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
         <v>250</v>
       </c>
-      <c r="B152" t="n">
+      <c r="B152">
         <v>11593</v>
       </c>
       <c r="C152" t="s">
         <v>329</v>
       </c>
-      <c r="D152" t="n">
+      <c r="D152">
         <v>2020</v>
       </c>
       <c r="E152" t="s">
@@ -10304,17 +10325,17 @@
         <v>26</v>
       </c>
     </row>
-    <row r="153">
+    <row r="153" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
         <v>250</v>
       </c>
-      <c r="B153" t="n">
+      <c r="B153">
         <v>11594</v>
       </c>
       <c r="C153" t="s">
         <v>329</v>
       </c>
-      <c r="D153" t="n">
+      <c r="D153">
         <v>2021</v>
       </c>
       <c r="E153" t="s">
@@ -10365,6 +10386,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>